--- a/rosters/.versions/2026-09/current.xlsx
+++ b/rosters/.versions/2026-09/current.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\80235\OneDrive - Oman Air\Desktop\Rosters\STAFF OPERATION SCHEDULE\Roster 5 x 3\2026\OPS\09 September 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86FB6E69-A3D0-490B-93D2-FCEF74DFD767}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF45F116-4E4E-43F7-81C0-00ABC9456A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{9736B67C-D61B-41E1-B07B-429B3D8AE9CC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="7" xr2:uid="{9736B67C-D61B-41E1-B07B-429B3D8AE9CC}"/>
   </bookViews>
   <sheets>
     <sheet name="Setting " sheetId="1" state="hidden" r:id="rId1"/>
@@ -60,7 +60,7 @@
     <author>Rodolfo C Magcaling</author>
   </authors>
   <commentList>
-    <comment ref="AA14" authorId="0" shapeId="0" xr:uid="{1EBB5B6D-0352-4A23-9ED2-F2E0E70220A3}">
+    <comment ref="AA13" authorId="0" shapeId="0" xr:uid="{6B6E4946-5944-4D4E-8DF1-4D0167F3A26B}">
       <text>
         <r>
           <rPr>
@@ -84,7 +84,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O15" authorId="0" shapeId="0" xr:uid="{4905B923-456E-4EFE-A920-6F24DFF13707}">
+    <comment ref="O14" authorId="0" shapeId="0" xr:uid="{C9E84FE0-8602-4951-8D11-1EFBD5EEEF79}">
       <text>
         <r>
           <rPr>
@@ -108,7 +108,55 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA17" authorId="0" shapeId="0" xr:uid="{8FC00881-4540-42AA-9B29-0A5A3DC2557E}">
+    <comment ref="G16" authorId="0" shapeId="0" xr:uid="{3C5282A6-6157-47E0-88FE-C1464CF30DAF}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Rodolfo C Magcaling:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+OT afternoon shift</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AC16" authorId="0" shapeId="0" xr:uid="{1AD5E512-E6BE-47CB-89B5-64300F799302}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Rodolfo C Magcaling:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Duty Supervisor on behalf of Talal on AL</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AA17" authorId="0" shapeId="0" xr:uid="{22FBD3AD-C73A-41DA-A3F4-584468922C20}">
       <text>
         <r>
           <rPr>
@@ -123,7 +171,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC17" authorId="0" shapeId="0" xr:uid="{AFFB3315-E1CA-40F0-B4FD-3878A4E20E5E}">
+    <comment ref="AC17" authorId="0" shapeId="0" xr:uid="{5AA9F3B4-DD81-4181-924F-F26F8E3B3656}">
       <text>
         <r>
           <rPr>
@@ -147,7 +195,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC18" authorId="0" shapeId="0" xr:uid="{4770E491-AC31-472B-85ED-D2B402B37E86}">
+    <comment ref="AC18" authorId="0" shapeId="0" xr:uid="{7865A005-5FBE-4572-8317-3B955363B236}">
       <text>
         <r>
           <rPr>
@@ -171,7 +219,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T19" authorId="0" shapeId="0" xr:uid="{7ADE4722-3FA0-4786-94F3-B322799A6549}">
+    <comment ref="T19" authorId="0" shapeId="0" xr:uid="{19C2C3B3-3262-40D4-9661-E06AD6ED71C4}">
       <text>
         <r>
           <rPr>
@@ -195,7 +243,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U19" authorId="0" shapeId="0" xr:uid="{A00305F7-9803-4E21-9D02-A1FE12F313CE}">
+    <comment ref="U19" authorId="0" shapeId="0" xr:uid="{D2C4990F-F17D-4508-99DC-6FBD8E812A3C}">
       <text>
         <r>
           <rPr>
@@ -219,7 +267,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA19" authorId="0" shapeId="0" xr:uid="{C41E95CB-7019-4591-84C9-82D2870C9AE1}">
+    <comment ref="AA19" authorId="0" shapeId="0" xr:uid="{64FB1926-9C87-4827-8275-A8E628B4E0EF}">
       <text>
         <r>
           <rPr>
@@ -243,7 +291,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O21" authorId="0" shapeId="0" xr:uid="{744187BB-B1CE-4951-AC5A-A34ACA110E9F}">
+    <comment ref="O21" authorId="0" shapeId="0" xr:uid="{701D0A0F-CBC0-466B-BA3F-89C3A8CDBA34}">
       <text>
         <r>
           <rPr>
@@ -267,7 +315,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W21" authorId="0" shapeId="0" xr:uid="{3595F630-AD7C-4295-B746-C62BBC526721}">
+    <comment ref="W21" authorId="0" shapeId="0" xr:uid="{3CE2B31C-4FD9-4E4D-8D37-6653B1D9FC1E}">
       <text>
         <r>
           <rPr>
@@ -291,7 +339,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X21" authorId="0" shapeId="0" xr:uid="{33870F4C-7CCC-4906-A775-468196A16034}">
+    <comment ref="X21" authorId="0" shapeId="0" xr:uid="{28A8C9E7-07D1-411F-8309-AB520EE22436}">
       <text>
         <r>
           <rPr>
@@ -315,7 +363,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y21" authorId="0" shapeId="0" xr:uid="{3E27BD5A-17C1-4B82-AF65-C46540246EF1}">
+    <comment ref="Y21" authorId="0" shapeId="0" xr:uid="{EFC57A12-2B4E-486C-8311-B11E7E4FA63D}">
       <text>
         <r>
           <rPr>
@@ -339,7 +387,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z21" authorId="0" shapeId="0" xr:uid="{C2722FAA-3242-41D8-8C16-169D316521F6}">
+    <comment ref="Z21" authorId="0" shapeId="0" xr:uid="{4B24ABC4-74FB-4AB2-9A4C-DAB27BF925BD}">
       <text>
         <r>
           <rPr>
@@ -363,7 +411,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H27" authorId="0" shapeId="0" xr:uid="{8EEBF7F8-CBB9-43F2-BDB4-AA82B13045CA}">
+    <comment ref="H27" authorId="0" shapeId="0" xr:uid="{718EB30D-ADD9-4FDD-B61F-E01397207FB5}">
       <text>
         <r>
           <rPr>
@@ -387,7 +435,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I27" authorId="0" shapeId="0" xr:uid="{ABB14FA9-B756-4D0F-B0D1-537D30AA3BDE}">
+    <comment ref="I27" authorId="0" shapeId="0" xr:uid="{285F05A2-A380-432D-9CEF-58A9D2E26493}">
       <text>
         <r>
           <rPr>
@@ -411,7 +459,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J27" authorId="0" shapeId="0" xr:uid="{4B1394F2-090A-4F5C-B346-E62A527132C0}">
+    <comment ref="J27" authorId="0" shapeId="0" xr:uid="{9CC2038E-5919-49AD-A0C3-28F0F9E9CDF6}">
       <text>
         <r>
           <rPr>
@@ -435,7 +483,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L27" authorId="0" shapeId="0" xr:uid="{7CF8067D-41F6-4C90-BDB2-BBC00A5A30B6}">
+    <comment ref="L27" authorId="0" shapeId="0" xr:uid="{603DF056-4C3C-4609-A3B5-65D5FC3FC1E7}">
       <text>
         <r>
           <rPr>
@@ -459,7 +507,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P27" authorId="0" shapeId="0" xr:uid="{33251460-6A5D-4E47-BAD8-062A12EEFA5A}">
+    <comment ref="P27" authorId="0" shapeId="0" xr:uid="{958DDFEC-743A-46DF-A9AD-23EEE8CF0129}">
       <text>
         <r>
           <rPr>
@@ -483,7 +531,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q27" authorId="0" shapeId="0" xr:uid="{493C2941-7804-43BA-B275-755BFFDEF4C9}">
+    <comment ref="Q27" authorId="0" shapeId="0" xr:uid="{AB5EFC1B-79A3-431D-B5FD-AEA440F546CB}">
       <text>
         <r>
           <rPr>
@@ -507,7 +555,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R27" authorId="0" shapeId="0" xr:uid="{250B283C-D5F3-4A83-9256-20D0D25D60FB}">
+    <comment ref="R27" authorId="0" shapeId="0" xr:uid="{9152039A-AF43-4806-9199-D82869D53273}">
       <text>
         <r>
           <rPr>
@@ -531,7 +579,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T27" authorId="0" shapeId="0" xr:uid="{F25AC58E-9B1F-49B9-B243-46E9779ECF7B}">
+    <comment ref="T27" authorId="0" shapeId="0" xr:uid="{EFE9C18B-2440-4ADB-B670-1B614A3182B7}">
       <text>
         <r>
           <rPr>
@@ -555,7 +603,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X27" authorId="0" shapeId="0" xr:uid="{B7D0CE85-ED2E-424E-B9DA-E946BDB57412}">
+    <comment ref="X27" authorId="0" shapeId="0" xr:uid="{D0BCDB19-131B-4EBD-9406-605D62B40873}">
       <text>
         <r>
           <rPr>
@@ -579,7 +627,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y27" authorId="0" shapeId="0" xr:uid="{6F36F915-3E2B-469C-82AC-484D4FEEE8DC}">
+    <comment ref="Y27" authorId="0" shapeId="0" xr:uid="{8DF3E339-4856-428B-A074-3E653B985861}">
       <text>
         <r>
           <rPr>
@@ -603,7 +651,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z27" authorId="0" shapeId="0" xr:uid="{28A1E41A-4D57-43D6-8B37-876931487654}">
+    <comment ref="Z27" authorId="0" shapeId="0" xr:uid="{3C000FFA-5B88-420F-8D26-973EF84BFD8D}">
       <text>
         <r>
           <rPr>
@@ -627,7 +675,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA27" authorId="0" shapeId="0" xr:uid="{07B5F314-53AE-4205-8478-11561356A97C}">
+    <comment ref="AA27" authorId="0" shapeId="0" xr:uid="{7090CD61-BE4D-4B32-A168-50C1A537FEFC}">
       <text>
         <r>
           <rPr>
@@ -651,7 +699,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB27" authorId="0" shapeId="0" xr:uid="{B1728C11-69A0-4501-AE1E-CAB5E6DA41A6}">
+    <comment ref="AB27" authorId="0" shapeId="0" xr:uid="{1A803ADD-99FD-45CC-9D42-9588F678B9CC}">
       <text>
         <r>
           <rPr>
@@ -675,7 +723,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC29" authorId="0" shapeId="0" xr:uid="{88B63BA4-017D-47EF-9827-4BFD5209C50A}">
+    <comment ref="AC29" authorId="0" shapeId="0" xr:uid="{51A68BC7-5D01-4A48-BC3C-75C2A54F557D}">
       <text>
         <r>
           <rPr>
@@ -699,7 +747,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AD29" authorId="0" shapeId="0" xr:uid="{44FB1DA9-D089-49EC-9220-A8AF5E1F8799}">
+    <comment ref="AD29" authorId="0" shapeId="0" xr:uid="{7203D845-51A7-4E73-9BD9-EAFC1622EF6D}">
       <text>
         <r>
           <rPr>
@@ -723,7 +771,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE29" authorId="0" shapeId="0" xr:uid="{6B13C32D-7384-4C42-860C-8A2DE2290E26}">
+    <comment ref="AE29" authorId="0" shapeId="0" xr:uid="{4A60EEC6-36D4-4948-9896-275139499CCE}">
       <text>
         <r>
           <rPr>
@@ -747,7 +795,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF29" authorId="0" shapeId="0" xr:uid="{83ACC754-332F-482F-B026-3AA0CA47C63A}">
+    <comment ref="AF29" authorId="0" shapeId="0" xr:uid="{C863A256-1462-46BB-A1EB-2C7B31150716}">
       <text>
         <r>
           <rPr>
@@ -771,7 +819,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AG29" authorId="0" shapeId="0" xr:uid="{BA3811F6-B304-4ACF-AF22-58B80729FA02}">
+    <comment ref="AG29" authorId="0" shapeId="0" xr:uid="{0DAE98EC-2F7E-4C29-A7BC-8856F4731813}">
       <text>
         <r>
           <rPr>
@@ -795,7 +843,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC33" authorId="0" shapeId="0" xr:uid="{A00AF1F2-9CFF-4DD8-A24A-C6428106C5FB}">
+    <comment ref="AC33" authorId="0" shapeId="0" xr:uid="{8E5AD391-C07D-4431-9490-6E2EAFAC9E9E}">
       <text>
         <r>
           <rPr>
@@ -819,7 +867,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA34" authorId="0" shapeId="0" xr:uid="{3B4B451E-284D-4D23-9581-492A1C5320BD}">
+    <comment ref="AA34" authorId="0" shapeId="0" xr:uid="{96A21065-AF39-4DCC-B7DD-A58E73F69F81}">
       <text>
         <r>
           <rPr>
@@ -843,7 +891,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC45" authorId="0" shapeId="0" xr:uid="{2C99F678-83C0-44F4-8DBB-D0C50554523C}">
+    <comment ref="AC45" authorId="0" shapeId="0" xr:uid="{20DF2D4F-3A74-4A68-AA02-8E4BBFD80571}">
       <text>
         <r>
           <rPr>
@@ -867,7 +915,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T46" authorId="0" shapeId="0" xr:uid="{DD6D2D46-2FE5-41A8-A27B-5B0197D298CF}">
+    <comment ref="T46" authorId="0" shapeId="0" xr:uid="{D2E11E04-6B0D-47AA-98DC-A6FC2BFB0163}">
       <text>
         <r>
           <rPr>
@@ -891,7 +939,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U46" authorId="0" shapeId="0" xr:uid="{047F4D1E-BA8E-4551-A97D-E8A92936EB9D}">
+    <comment ref="U46" authorId="0" shapeId="0" xr:uid="{A4A89B69-6724-42BE-8FDF-DFD9C8C56E5D}">
       <text>
         <r>
           <rPr>
@@ -915,7 +963,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB50" authorId="0" shapeId="0" xr:uid="{7BE61B37-5885-49E0-B78B-9E027216844E}">
+    <comment ref="AB50" authorId="0" shapeId="0" xr:uid="{F30FD6B8-8570-4074-8EC0-286DDF1968C4}">
       <text>
         <r>
           <rPr>
@@ -939,7 +987,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC52" authorId="0" shapeId="0" xr:uid="{73D5DC2B-4AE7-4D9C-940D-83300E165A1B}">
+    <comment ref="AC52" authorId="0" shapeId="0" xr:uid="{9CD2152B-BDFB-4622-8D90-A0A58CC59096}">
       <text>
         <r>
           <rPr>
@@ -963,7 +1011,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB65" authorId="0" shapeId="0" xr:uid="{6142BB60-B6C4-475F-BE4F-5EE071FE994D}">
+    <comment ref="AB65" authorId="0" shapeId="0" xr:uid="{54FAF407-EB9D-47F5-AFD6-96787DA05719}">
       <text>
         <r>
           <rPr>
@@ -987,7 +1035,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K66" authorId="0" shapeId="0" xr:uid="{C45431AE-E57F-4496-BC69-3B85780A1C73}">
+    <comment ref="K66" authorId="0" shapeId="0" xr:uid="{A24A3F7C-2E9E-4725-984F-CBB2C35C2579}">
       <text>
         <r>
           <rPr>
@@ -1011,7 +1059,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M68" authorId="0" shapeId="0" xr:uid="{A89E092E-3898-424B-9CDF-90F521C57105}">
+    <comment ref="M68" authorId="0" shapeId="0" xr:uid="{63D39C3E-83B0-4D18-85F7-A587B56C760F}">
       <text>
         <r>
           <rPr>
@@ -1035,7 +1083,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB75" authorId="0" shapeId="0" xr:uid="{BAAFE4F3-4478-4C19-8CBA-26E08FAE4331}">
+    <comment ref="AB75" authorId="0" shapeId="0" xr:uid="{2AAC95FA-C3D2-4305-9C8D-86CA9A77348E}">
       <text>
         <r>
           <rPr>
@@ -1583,7 +1631,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC5" authorId="0" shapeId="0" xr:uid="{3C51B2B4-8B00-476D-A0FE-F2FF79CFC7F6}">
+    <comment ref="AC5" authorId="0" shapeId="0" xr:uid="{6BB92B2D-9A02-498E-A94B-4D414E5FBEB9}">
       <text>
         <r>
           <rPr>
@@ -1607,7 +1655,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA6" authorId="0" shapeId="0" xr:uid="{B9BAD5C0-4046-4DB2-AF2D-CC15EA189E70}">
+    <comment ref="AA6" authorId="0" shapeId="0" xr:uid="{2563573C-CC27-4B39-8466-748C3626DAF8}">
       <text>
         <r>
           <rPr>
@@ -1622,7 +1670,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC6" authorId="0" shapeId="0" xr:uid="{85F2E8C3-6DA5-426C-AE4D-38C89776CB72}">
+    <comment ref="AC6" authorId="0" shapeId="0" xr:uid="{9F04E234-B17D-4147-B2A3-245EDFB99BC3}">
       <text>
         <r>
           <rPr>
@@ -1646,7 +1694,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC7" authorId="0" shapeId="0" xr:uid="{5696D594-4952-4F3D-BEC6-EA37137B0782}">
+    <comment ref="AC7" authorId="0" shapeId="0" xr:uid="{B315738E-D90B-414F-AD95-E4427DF83B9A}">
       <text>
         <r>
           <rPr>
@@ -1670,7 +1718,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T8" authorId="0" shapeId="0" xr:uid="{E6B8EF32-EEF2-422B-AB26-D67524B941FC}">
+    <comment ref="T8" authorId="0" shapeId="0" xr:uid="{6EA5A3C2-3005-46CB-BBE5-5577D79DD4FB}">
       <text>
         <r>
           <rPr>
@@ -1694,7 +1742,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U8" authorId="0" shapeId="0" xr:uid="{341F5B49-2A33-437C-8300-421FBA04C6B2}">
+    <comment ref="U8" authorId="0" shapeId="0" xr:uid="{B96AD9A5-1871-46B9-A62B-59CCCB272EFF}">
       <text>
         <r>
           <rPr>
@@ -1718,7 +1766,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA8" authorId="0" shapeId="0" xr:uid="{D6DA83F4-C7CC-49DC-AB01-D5F8797F4BC3}">
+    <comment ref="AA8" authorId="0" shapeId="0" xr:uid="{22BCA0C5-6CC4-46E4-BFE4-6D5AB00D3651}">
       <text>
         <r>
           <rPr>
@@ -1766,7 +1814,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W10" authorId="0" shapeId="0" xr:uid="{51F4D771-098C-4F85-9AFB-24E3B4E1FDC6}">
+    <comment ref="W10" authorId="0" shapeId="0" xr:uid="{792F05BB-956A-4C13-8FD7-A8328DB10956}">
       <text>
         <r>
           <rPr>
@@ -1790,7 +1838,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X10" authorId="0" shapeId="0" xr:uid="{E00ECF63-FB7B-4743-A01D-3CEAEE4C01E3}">
+    <comment ref="X10" authorId="0" shapeId="0" xr:uid="{A10EA4C3-AAFD-4FB6-A14C-7BECC3BB7D16}">
       <text>
         <r>
           <rPr>
@@ -1814,7 +1862,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y10" authorId="0" shapeId="0" xr:uid="{FD554C21-0E16-4475-9879-70B5DD7A0FBF}">
+    <comment ref="Y10" authorId="0" shapeId="0" xr:uid="{4A4E9C76-9938-47BE-8D34-93DDC2906719}">
       <text>
         <r>
           <rPr>
@@ -1838,7 +1886,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z10" authorId="0" shapeId="0" xr:uid="{CEE495E4-6DED-434C-8419-3798FC7EA215}">
+    <comment ref="Z10" authorId="0" shapeId="0" xr:uid="{552B5588-3596-4617-86C6-B1D063D1F8B5}">
       <text>
         <r>
           <rPr>
@@ -2030,7 +2078,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T16" authorId="0" shapeId="0" xr:uid="{6A6F8988-0F12-4648-A504-5CB31D799C3F}">
+    <comment ref="T16" authorId="0" shapeId="0" xr:uid="{CA00441D-8270-4E77-BD8B-6A7B718BCA44}">
       <text>
         <r>
           <rPr>
@@ -2054,7 +2102,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X16" authorId="0" shapeId="0" xr:uid="{25CC7708-8415-46D0-A362-D06CDC8A1900}">
+    <comment ref="X16" authorId="0" shapeId="0" xr:uid="{EA367565-3161-43E4-B804-F7C21A00BD10}">
       <text>
         <r>
           <rPr>
@@ -2078,7 +2126,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y16" authorId="0" shapeId="0" xr:uid="{12B7BCD6-B072-46B2-88A8-C9B9A7745AB9}">
+    <comment ref="Y16" authorId="0" shapeId="0" xr:uid="{EB7C12A5-2E35-48D5-A191-CF0DDE07EF6A}">
       <text>
         <r>
           <rPr>
@@ -2102,7 +2150,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z16" authorId="0" shapeId="0" xr:uid="{520E86AC-DC6A-4F2C-A019-9C57C68CDB5A}">
+    <comment ref="Z16" authorId="0" shapeId="0" xr:uid="{DD915229-C363-4911-8E74-99549302A4B3}">
       <text>
         <r>
           <rPr>
@@ -2126,7 +2174,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA16" authorId="0" shapeId="0" xr:uid="{0DC37C22-CB6D-4FC9-9942-C73C1577409E}">
+    <comment ref="AA16" authorId="0" shapeId="0" xr:uid="{EF82B4CC-075B-4DA1-AF08-C16C953DF0D8}">
       <text>
         <r>
           <rPr>
@@ -2150,7 +2198,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB16" authorId="0" shapeId="0" xr:uid="{DB11432F-085F-43CE-9C69-0DCC9D352B90}">
+    <comment ref="AB16" authorId="0" shapeId="0" xr:uid="{C2A19ADC-51B6-4E0E-8FEF-9C05EEEF600A}">
       <text>
         <r>
           <rPr>
@@ -2174,7 +2222,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC18" authorId="0" shapeId="0" xr:uid="{67199866-0EE3-4B07-8F97-1791C5BAEB97}">
+    <comment ref="AC18" authorId="0" shapeId="0" xr:uid="{C82FC553-A114-458F-96D7-F57EA581FB94}">
       <text>
         <r>
           <rPr>
@@ -2198,7 +2246,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AD18" authorId="0" shapeId="0" xr:uid="{41B6637C-EB59-46A2-B357-7F73DEF27009}">
+    <comment ref="AD18" authorId="0" shapeId="0" xr:uid="{152092C0-9724-4CAE-BC82-A3CC2831DF20}">
       <text>
         <r>
           <rPr>
@@ -2222,7 +2270,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE18" authorId="0" shapeId="0" xr:uid="{1B0DAFD0-A9DD-49D1-9127-7EBACF24AB90}">
+    <comment ref="AE18" authorId="0" shapeId="0" xr:uid="{B5455FE5-36D7-444C-B879-3392116337A8}">
       <text>
         <r>
           <rPr>
@@ -2246,7 +2294,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF18" authorId="0" shapeId="0" xr:uid="{15468DF9-7D09-42B6-AA35-851B0169B99C}">
+    <comment ref="AF18" authorId="0" shapeId="0" xr:uid="{C526C77B-257B-46A7-BA45-869609AD7A16}">
       <text>
         <r>
           <rPr>
@@ -2270,7 +2318,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AG18" authorId="0" shapeId="0" xr:uid="{5885C43D-D753-4981-B07C-2FD303A5FF9D}">
+    <comment ref="AG18" authorId="0" shapeId="0" xr:uid="{07A007A6-30BA-45AE-9BEC-5FFC8A5888FF}">
       <text>
         <r>
           <rPr>
@@ -2304,7 +2352,7 @@
     <author>Rodolfo C Magcaling</author>
   </authors>
   <commentList>
-    <comment ref="AC7" authorId="0" shapeId="0" xr:uid="{73F95721-230B-4A2B-83F3-991A4D22B8A2}">
+    <comment ref="AC7" authorId="0" shapeId="0" xr:uid="{0BDC4485-0C4E-410A-B63E-99A602549FFF}">
       <text>
         <r>
           <rPr>
@@ -2328,7 +2376,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA8" authorId="0" shapeId="0" xr:uid="{080CA417-2DEE-4831-96C5-DC7347719B3E}">
+    <comment ref="AA8" authorId="0" shapeId="0" xr:uid="{9FFEC7A3-0701-4407-AB14-891B152E4B85}">
       <text>
         <r>
           <rPr>
@@ -2352,7 +2400,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC19" authorId="0" shapeId="0" xr:uid="{6AE33FE0-537E-497A-826E-CFA713E15D24}">
+    <comment ref="AC19" authorId="0" shapeId="0" xr:uid="{9A99B176-2858-4CF6-94A4-712D6C2AC8A6}">
       <text>
         <r>
           <rPr>
@@ -2376,7 +2424,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T20" authorId="0" shapeId="0" xr:uid="{8B2E0903-FEA4-4BC0-9D6D-CEB300E37E96}">
+    <comment ref="T20" authorId="0" shapeId="0" xr:uid="{4FE4B414-D036-4F34-8918-3AF8CE2AFC15}">
       <text>
         <r>
           <rPr>
@@ -2400,7 +2448,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U20" authorId="0" shapeId="0" xr:uid="{237A9B1C-C64E-4C6E-8016-B23A43DA54B1}">
+    <comment ref="U20" authorId="0" shapeId="0" xr:uid="{3C3CBF82-B46E-458A-8395-686E659068B9}">
       <text>
         <r>
           <rPr>
@@ -2424,7 +2472,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB24" authorId="0" shapeId="0" xr:uid="{073BCEB9-18D1-45A3-B584-42E8AA30C2BD}">
+    <comment ref="AB24" authorId="0" shapeId="0" xr:uid="{613074F2-99ED-4C78-9F94-ABE5EEC89CE6}">
       <text>
         <r>
           <rPr>
@@ -2448,7 +2496,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC26" authorId="0" shapeId="0" xr:uid="{0A1D00A2-D1EB-4330-BD4B-BAB4912AE288}">
+    <comment ref="AC26" authorId="0" shapeId="0" xr:uid="{A65CB334-F2CA-458A-89E3-FA9E0F015617}">
       <text>
         <r>
           <rPr>
@@ -2482,7 +2530,7 @@
     <author>Rodolfo C Magcaling</author>
   </authors>
   <commentList>
-    <comment ref="AB8" authorId="0" shapeId="0" xr:uid="{1FC8659B-2C5F-44C9-98E3-8D8A397DB9A7}">
+    <comment ref="AB8" authorId="0" shapeId="0" xr:uid="{E91A11DE-566F-4673-908E-FB754F672D8A}">
       <text>
         <r>
           <rPr>
@@ -2554,7 +2602,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB18" authorId="0" shapeId="0" xr:uid="{D4B3FDB0-2A2B-4924-93B9-B68E9D1781EC}">
+    <comment ref="AB18" authorId="0" shapeId="0" xr:uid="{F0D55AE9-D9AA-4D64-ABC9-E16A6AAA8834}">
       <text>
         <r>
           <rPr>
@@ -2583,7 +2631,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5478" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5448" uniqueCount="256">
   <si>
     <t>Month List</t>
   </si>
@@ -5106,7 +5154,704 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="238">
+  <dxfs count="403">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color auto="1"/>
@@ -5258,6 +6003,808 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6804,6 +8351,16 @@
       </font>
       <fill>
         <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
           <bgColor theme="8" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
@@ -6823,16 +8380,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="0" tint="-0.14996795556505021"/>
@@ -6843,6 +8390,16 @@
       <fill>
         <patternFill>
           <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6868,18 +8425,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFC00000"/>
+        <color auto="1"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6915,13 +8465,11 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
+        <color rgb="FFC00000"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFF00"/>
+          <bgColor theme="9" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6936,22 +8484,21 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
+          <bgColor theme="8" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <color auto="1"/>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
+          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6968,17 +8515,7 @@
       </font>
       <fill>
         <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
+          <bgColor rgb="FF7030A0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -7004,16 +8541,6 @@
     </dxf>
     <dxf>
       <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FFC00000"/>
       </font>
       <fill>
@@ -7033,6 +8560,33 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.79998168889431442"/>
@@ -7040,9 +8594,29 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
       <fill>
         <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -7095,28 +8669,12 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFC00000"/>
+        <color auto="1"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
+          <fgColor auto="1"/>
+          <bgColor theme="5" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -7149,42 +8707,11 @@
     </dxf>
     <dxf>
       <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor auto="1"/>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FFC00000"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
+          <bgColor theme="7" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -7211,13 +8738,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
@@ -7225,7 +8745,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
+          <bgColor theme="8" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -7246,7 +8766,34 @@
       </font>
       <fill>
         <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -13296,26 +14843,26 @@
     <mergeCell ref="X4:Z4"/>
   </mergeCells>
   <conditionalFormatting sqref="E8:AI37 AK8:AN37 E39:AI42">
-    <cfRule type="expression" dxfId="237" priority="4">
+    <cfRule type="expression" dxfId="402" priority="4">
       <formula>LEFT(E8,1)="N"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="236" priority="5">
+    <cfRule type="expression" dxfId="401" priority="5">
       <formula>LEFT(E8,1)="A"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="235" priority="7">
+    <cfRule type="expression" dxfId="400" priority="7">
       <formula>LEFT(E8,1)="M"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="234" priority="8">
+    <cfRule type="expression" dxfId="399" priority="8">
       <formula>LEFT(E8,1)="D"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E39:AI42 E8:AI37 AK8:AN37">
-    <cfRule type="expression" dxfId="233" priority="3">
+    <cfRule type="expression" dxfId="398" priority="3">
       <formula>LEFT(E8,1)="O"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E39:AI42">
-    <cfRule type="expression" dxfId="232" priority="1">
+    <cfRule type="expression" dxfId="397" priority="1">
       <formula>ISEVEN(ROW($E39))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14209,7 +15756,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="2:42" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:42" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B10" s="37" t="s">
         <v>213</v>
       </c>
@@ -14337,95 +15884,95 @@
         <v>157</v>
       </c>
       <c r="D11" s="172"/>
-      <c r="F11" s="42" t="s">
-        <v>196</v>
-      </c>
-      <c r="G11" s="42" t="s">
-        <v>220</v>
-      </c>
-      <c r="H11" s="42" t="s">
-        <v>221</v>
-      </c>
-      <c r="I11" s="42" t="s">
-        <v>221</v>
-      </c>
-      <c r="J11" s="42" t="s">
-        <v>221</v>
-      </c>
-      <c r="K11" s="42" t="s">
-        <v>196</v>
-      </c>
-      <c r="L11" s="42" t="s">
-        <v>196</v>
-      </c>
-      <c r="M11" s="42" t="s">
-        <v>197</v>
-      </c>
-      <c r="N11" s="42" t="s">
-        <v>197</v>
-      </c>
-      <c r="O11" s="42" t="s">
-        <v>220</v>
-      </c>
-      <c r="P11" s="42" t="s">
-        <v>221</v>
-      </c>
-      <c r="Q11" s="42" t="s">
-        <v>221</v>
-      </c>
-      <c r="R11" s="42" t="s">
-        <v>221</v>
-      </c>
-      <c r="S11" s="42" t="s">
-        <v>196</v>
-      </c>
-      <c r="T11" s="42" t="s">
-        <v>196</v>
-      </c>
-      <c r="U11" s="42" t="s">
-        <v>197</v>
-      </c>
-      <c r="V11" s="42" t="s">
-        <v>197</v>
-      </c>
-      <c r="W11" s="42" t="s">
-        <v>220</v>
-      </c>
-      <c r="X11" s="42" t="s">
-        <v>221</v>
-      </c>
-      <c r="Y11" s="42" t="s">
-        <v>221</v>
-      </c>
-      <c r="Z11" s="42" t="s">
-        <v>221</v>
-      </c>
-      <c r="AA11" s="42" t="s">
-        <v>196</v>
-      </c>
-      <c r="AB11" s="42" t="s">
-        <v>196</v>
-      </c>
-      <c r="AC11" s="42" t="s">
-        <v>197</v>
-      </c>
-      <c r="AD11" s="42" t="s">
-        <v>197</v>
-      </c>
-      <c r="AE11" s="42" t="s">
-        <v>220</v>
-      </c>
-      <c r="AF11" s="42" t="s">
-        <v>221</v>
-      </c>
-      <c r="AG11" s="42" t="s">
-        <v>221</v>
-      </c>
-      <c r="AH11" s="42" t="s">
-        <v>221</v>
-      </c>
-      <c r="AI11" s="42" t="s">
-        <v>196</v>
+      <c r="F11" s="49" t="s">
+        <v>221</v>
+      </c>
+      <c r="G11" s="49" t="s">
+        <v>221</v>
+      </c>
+      <c r="H11" s="49" t="s">
+        <v>222</v>
+      </c>
+      <c r="I11" s="49" t="s">
+        <v>222</v>
+      </c>
+      <c r="J11" s="49" t="s">
+        <v>222</v>
+      </c>
+      <c r="K11" s="49" t="s">
+        <v>222</v>
+      </c>
+      <c r="L11" s="49" t="s">
+        <v>222</v>
+      </c>
+      <c r="M11" s="49" t="s">
+        <v>222</v>
+      </c>
+      <c r="N11" s="49" t="s">
+        <v>222</v>
+      </c>
+      <c r="O11" s="49" t="s">
+        <v>222</v>
+      </c>
+      <c r="P11" s="49" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q11" s="49" t="s">
+        <v>222</v>
+      </c>
+      <c r="R11" s="49" t="s">
+        <v>222</v>
+      </c>
+      <c r="S11" s="49" t="s">
+        <v>222</v>
+      </c>
+      <c r="T11" s="49" t="s">
+        <v>222</v>
+      </c>
+      <c r="U11" s="49" t="s">
+        <v>222</v>
+      </c>
+      <c r="V11" s="49" t="s">
+        <v>222</v>
+      </c>
+      <c r="W11" s="49" t="s">
+        <v>222</v>
+      </c>
+      <c r="X11" s="49" t="s">
+        <v>222</v>
+      </c>
+      <c r="Y11" s="49" t="s">
+        <v>222</v>
+      </c>
+      <c r="Z11" s="49" t="s">
+        <v>222</v>
+      </c>
+      <c r="AA11" s="49" t="s">
+        <v>222</v>
+      </c>
+      <c r="AB11" s="49" t="s">
+        <v>222</v>
+      </c>
+      <c r="AC11" s="49" t="s">
+        <v>221</v>
+      </c>
+      <c r="AD11" s="49" t="s">
+        <v>221</v>
+      </c>
+      <c r="AE11" s="49" t="s">
+        <v>221</v>
+      </c>
+      <c r="AF11" s="49" t="s">
+        <v>196</v>
+      </c>
+      <c r="AG11" s="49" t="s">
+        <v>196</v>
+      </c>
+      <c r="AH11" s="49" t="s">
+        <v>197</v>
+      </c>
+      <c r="AI11" s="49" t="s">
+        <v>197</v>
       </c>
       <c r="AJ11" s="49"/>
       <c r="AL11" s="48">
@@ -14434,19 +15981,19 @@
       </c>
       <c r="AM11" s="48">
         <f t="shared" si="6"/>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AN11" s="48">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AO11" s="48">
         <f t="shared" si="8"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AP11" s="48">
         <f t="shared" si="9"/>
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="2:42" ht="18.75" x14ac:dyDescent="0.25">
@@ -14461,52 +16008,52 @@
         <v>221</v>
       </c>
       <c r="G12" s="49" t="s">
-        <v>221</v>
+        <v>196</v>
       </c>
       <c r="H12" s="49" t="s">
-        <v>222</v>
+        <v>197</v>
       </c>
       <c r="I12" s="49" t="s">
-        <v>222</v>
+        <v>197</v>
       </c>
       <c r="J12" s="49" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K12" s="49" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="L12" s="49" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M12" s="49" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="N12" s="49" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O12" s="49" t="s">
-        <v>222</v>
+        <v>196</v>
       </c>
       <c r="P12" s="49" t="s">
-        <v>222</v>
+        <v>197</v>
       </c>
       <c r="Q12" s="49" t="s">
-        <v>222</v>
+        <v>197</v>
       </c>
       <c r="R12" s="49" t="s">
-        <v>222</v>
-      </c>
-      <c r="S12" s="49" t="s">
-        <v>222</v>
+        <v>220</v>
+      </c>
+      <c r="S12" s="130" t="s">
+        <v>220</v>
       </c>
       <c r="T12" s="49" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="U12" s="49" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="V12" s="49" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="W12" s="49" t="s">
         <v>222</v>
@@ -14533,19 +16080,19 @@
         <v>221</v>
       </c>
       <c r="AE12" s="49" t="s">
-        <v>221</v>
+        <v>196</v>
       </c>
       <c r="AF12" s="49" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG12" s="49" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AH12" s="49" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="AI12" s="49" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="AJ12" s="49"/>
       <c r="AL12" s="48">
@@ -14554,19 +16101,19 @@
       </c>
       <c r="AM12" s="48">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN12" s="48">
         <f t="shared" si="7"/>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AO12" s="48">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AP12" s="48">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="2:42" ht="18.75" x14ac:dyDescent="0.25">
@@ -14578,94 +16125,94 @@
       </c>
       <c r="D13" s="172"/>
       <c r="F13" s="49" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G13" s="49" t="s">
-        <v>196</v>
+        <v>221</v>
       </c>
       <c r="H13" s="49" t="s">
-        <v>197</v>
+        <v>221</v>
       </c>
       <c r="I13" s="49" t="s">
-        <v>197</v>
+        <v>221</v>
       </c>
       <c r="J13" s="49" t="s">
-        <v>220</v>
+        <v>196</v>
       </c>
       <c r="K13" s="49" t="s">
-        <v>220</v>
+        <v>197</v>
       </c>
       <c r="L13" s="49" t="s">
-        <v>221</v>
+        <v>197</v>
       </c>
       <c r="M13" s="49" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="N13" s="49" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="O13" s="49" t="s">
-        <v>196</v>
+        <v>221</v>
       </c>
       <c r="P13" s="49" t="s">
-        <v>197</v>
+        <v>221</v>
       </c>
       <c r="Q13" s="49" t="s">
-        <v>197</v>
+        <v>221</v>
       </c>
       <c r="R13" s="49" t="s">
-        <v>220</v>
-      </c>
-      <c r="S13" s="130" t="s">
-        <v>220</v>
+        <v>196</v>
+      </c>
+      <c r="S13" s="49" t="s">
+        <v>197</v>
       </c>
       <c r="T13" s="49" t="s">
-        <v>221</v>
+        <v>197</v>
       </c>
       <c r="U13" s="49" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="V13" s="49" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="W13" s="49" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="X13" s="49" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Y13" s="49" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Z13" s="49" t="s">
-        <v>222</v>
+        <v>196</v>
       </c>
       <c r="AA13" s="49" t="s">
-        <v>222</v>
+        <v>126</v>
       </c>
       <c r="AB13" s="49" t="s">
-        <v>222</v>
+        <v>197</v>
       </c>
       <c r="AC13" s="49" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AD13" s="49" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AE13" s="49" t="s">
-        <v>196</v>
+        <v>221</v>
       </c>
       <c r="AF13" s="49" t="s">
-        <v>197</v>
+        <v>221</v>
       </c>
       <c r="AG13" s="49" t="s">
-        <v>197</v>
+        <v>221</v>
       </c>
       <c r="AH13" s="49" t="s">
-        <v>220</v>
+        <v>196</v>
       </c>
       <c r="AI13" s="49" t="s">
-        <v>220</v>
+        <v>197</v>
       </c>
       <c r="AJ13" s="49"/>
       <c r="AL13" s="48">
@@ -14674,7 +16221,7 @@
       </c>
       <c r="AM13" s="48">
         <f t="shared" si="6"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN13" s="48">
         <f t="shared" si="7"/>
@@ -14682,11 +16229,11 @@
       </c>
       <c r="AO13" s="48">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP13" s="48">
         <f t="shared" si="9"/>
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="2:42" ht="18.75" x14ac:dyDescent="0.25">
@@ -14698,94 +16245,94 @@
       </c>
       <c r="D14" s="172"/>
       <c r="F14" s="49" t="s">
-        <v>220</v>
+        <v>197</v>
       </c>
       <c r="G14" s="49" t="s">
-        <v>221</v>
+        <v>197</v>
       </c>
       <c r="H14" s="49" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I14" s="49" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="J14" s="49" t="s">
-        <v>196</v>
+        <v>221</v>
       </c>
       <c r="K14" s="49" t="s">
-        <v>197</v>
+        <v>221</v>
       </c>
       <c r="L14" s="49" t="s">
-        <v>197</v>
+        <v>221</v>
       </c>
       <c r="M14" s="49" t="s">
-        <v>220</v>
+        <v>196</v>
       </c>
       <c r="N14" s="49" t="s">
-        <v>220</v>
+        <v>196</v>
       </c>
       <c r="O14" s="49" t="s">
-        <v>221</v>
+        <v>126</v>
       </c>
       <c r="P14" s="49" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Q14" s="49" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="R14" s="49" t="s">
-        <v>196</v>
+        <v>221</v>
       </c>
       <c r="S14" s="49" t="s">
-        <v>197</v>
+        <v>221</v>
       </c>
       <c r="T14" s="49" t="s">
-        <v>197</v>
+        <v>221</v>
       </c>
       <c r="U14" s="49" t="s">
-        <v>220</v>
+        <v>196</v>
       </c>
       <c r="V14" s="49" t="s">
-        <v>220</v>
+        <v>196</v>
       </c>
       <c r="W14" s="49" t="s">
-        <v>221</v>
+        <v>197</v>
       </c>
       <c r="X14" s="49" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Y14" s="49" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Z14" s="49" t="s">
-        <v>196</v>
+        <v>221</v>
       </c>
       <c r="AA14" s="49" t="s">
-        <v>126</v>
+        <v>245</v>
       </c>
       <c r="AB14" s="49" t="s">
-        <v>197</v>
+        <v>221</v>
       </c>
       <c r="AC14" s="49" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AD14" s="49" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AE14" s="49" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AF14" s="49" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG14" s="49" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AH14" s="49" t="s">
-        <v>196</v>
+        <v>222</v>
       </c>
       <c r="AI14" s="49" t="s">
-        <v>197</v>
+        <v>221</v>
       </c>
       <c r="AJ14" s="49"/>
       <c r="AK14" s="77"/>
@@ -14799,15 +16346,15 @@
       </c>
       <c r="AN14" s="48">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AO14" s="48">
         <f t="shared" si="8"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP14" s="48">
         <f t="shared" si="9"/>
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="2:42" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -14818,95 +16365,95 @@
         <v>161</v>
       </c>
       <c r="D15" s="172"/>
-      <c r="F15" s="49" t="s">
-        <v>197</v>
-      </c>
-      <c r="G15" s="49" t="s">
-        <v>197</v>
-      </c>
-      <c r="H15" s="49" t="s">
-        <v>220</v>
-      </c>
-      <c r="I15" s="49" t="s">
-        <v>220</v>
-      </c>
-      <c r="J15" s="49" t="s">
-        <v>221</v>
-      </c>
-      <c r="K15" s="49" t="s">
-        <v>221</v>
-      </c>
-      <c r="L15" s="49" t="s">
-        <v>221</v>
-      </c>
-      <c r="M15" s="49" t="s">
-        <v>196</v>
-      </c>
-      <c r="N15" s="49" t="s">
-        <v>196</v>
-      </c>
-      <c r="O15" s="49" t="s">
-        <v>126</v>
-      </c>
-      <c r="P15" s="49" t="s">
-        <v>220</v>
-      </c>
-      <c r="Q15" s="49" t="s">
-        <v>220</v>
-      </c>
-      <c r="R15" s="49" t="s">
-        <v>221</v>
-      </c>
-      <c r="S15" s="49" t="s">
-        <v>221</v>
-      </c>
-      <c r="T15" s="49" t="s">
-        <v>221</v>
-      </c>
-      <c r="U15" s="49" t="s">
-        <v>196</v>
-      </c>
-      <c r="V15" s="49" t="s">
-        <v>196</v>
-      </c>
-      <c r="W15" s="49" t="s">
-        <v>197</v>
-      </c>
-      <c r="X15" s="49" t="s">
-        <v>220</v>
-      </c>
-      <c r="Y15" s="49" t="s">
-        <v>220</v>
-      </c>
-      <c r="Z15" s="49" t="s">
-        <v>221</v>
-      </c>
-      <c r="AA15" s="49" t="s">
-        <v>245</v>
-      </c>
-      <c r="AB15" s="49" t="s">
-        <v>221</v>
-      </c>
-      <c r="AC15" s="49" t="s">
+      <c r="F15" s="55" t="s">
+        <v>196</v>
+      </c>
+      <c r="G15" s="55" t="s">
+        <v>196</v>
+      </c>
+      <c r="H15" s="55" t="s">
+        <v>196</v>
+      </c>
+      <c r="I15" s="55" t="s">
+        <v>221</v>
+      </c>
+      <c r="J15" s="55" t="s">
+        <v>221</v>
+      </c>
+      <c r="K15" s="55" t="s">
+        <v>196</v>
+      </c>
+      <c r="L15" s="55" t="s">
+        <v>196</v>
+      </c>
+      <c r="M15" s="55" t="s">
+        <v>196</v>
+      </c>
+      <c r="N15" s="55" t="s">
+        <v>196</v>
+      </c>
+      <c r="O15" s="55" t="s">
+        <v>196</v>
+      </c>
+      <c r="P15" s="55" t="s">
+        <v>221</v>
+      </c>
+      <c r="Q15" s="55" t="s">
+        <v>221</v>
+      </c>
+      <c r="R15" s="55" t="s">
         <v>222</v>
       </c>
-      <c r="AD15" s="49" t="s">
+      <c r="S15" s="55" t="s">
         <v>222</v>
       </c>
-      <c r="AE15" s="49" t="s">
+      <c r="T15" s="55" t="s">
         <v>222</v>
       </c>
-      <c r="AF15" s="49" t="s">
+      <c r="U15" s="55" t="s">
         <v>222</v>
       </c>
-      <c r="AG15" s="49" t="s">
+      <c r="V15" s="55" t="s">
         <v>222</v>
       </c>
-      <c r="AH15" s="49" t="s">
-        <v>222</v>
-      </c>
-      <c r="AI15" s="49" t="s">
-        <v>221</v>
+      <c r="W15" s="55" t="s">
+        <v>221</v>
+      </c>
+      <c r="X15" s="55" t="s">
+        <v>221</v>
+      </c>
+      <c r="Y15" s="55" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z15" s="55" t="s">
+        <v>196</v>
+      </c>
+      <c r="AA15" s="55" t="s">
+        <v>196</v>
+      </c>
+      <c r="AB15" s="55" t="s">
+        <v>196</v>
+      </c>
+      <c r="AC15" s="55" t="s">
+        <v>196</v>
+      </c>
+      <c r="AD15" s="55" t="s">
+        <v>221</v>
+      </c>
+      <c r="AE15" s="55" t="s">
+        <v>221</v>
+      </c>
+      <c r="AF15" s="55" t="s">
+        <v>196</v>
+      </c>
+      <c r="AG15" s="55" t="s">
+        <v>196</v>
+      </c>
+      <c r="AH15" s="55" t="s">
+        <v>196</v>
+      </c>
+      <c r="AI15" s="55" t="s">
+        <v>196</v>
       </c>
       <c r="AJ15" s="55"/>
       <c r="AL15" s="48">
@@ -14915,22 +16462,22 @@
       </c>
       <c r="AM15" s="48">
         <f t="shared" si="6"/>
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="AN15" s="48">
         <f t="shared" si="7"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO15" s="48">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AP15" s="48">
         <f t="shared" si="9"/>
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
-    <row r="16" spans="2:42" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:42" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B16" s="37" t="s">
         <v>214</v>
       </c>
@@ -14939,95 +16486,95 @@
       </c>
       <c r="D16" s="183"/>
       <c r="E16" s="76"/>
-      <c r="F16" s="55" t="s">
-        <v>196</v>
-      </c>
-      <c r="G16" s="55" t="s">
-        <v>196</v>
-      </c>
-      <c r="H16" s="55" t="s">
-        <v>196</v>
-      </c>
-      <c r="I16" s="55" t="s">
-        <v>221</v>
-      </c>
-      <c r="J16" s="55" t="s">
-        <v>221</v>
-      </c>
-      <c r="K16" s="55" t="s">
-        <v>196</v>
-      </c>
-      <c r="L16" s="55" t="s">
-        <v>196</v>
-      </c>
-      <c r="M16" s="55" t="s">
-        <v>196</v>
-      </c>
-      <c r="N16" s="55" t="s">
-        <v>196</v>
-      </c>
-      <c r="O16" s="55" t="s">
-        <v>196</v>
-      </c>
-      <c r="P16" s="55" t="s">
-        <v>221</v>
-      </c>
-      <c r="Q16" s="55" t="s">
-        <v>221</v>
-      </c>
-      <c r="R16" s="55" t="s">
+      <c r="F16" s="98" t="s">
+        <v>197</v>
+      </c>
+      <c r="G16" s="99" t="s">
+        <v>196</v>
+      </c>
+      <c r="H16" s="99" t="s">
+        <v>220</v>
+      </c>
+      <c r="I16" s="98" t="s">
+        <v>221</v>
+      </c>
+      <c r="J16" s="98" t="s">
+        <v>221</v>
+      </c>
+      <c r="K16" s="98" t="s">
+        <v>221</v>
+      </c>
+      <c r="L16" s="98" t="s">
         <v>222</v>
       </c>
-      <c r="S16" s="55" t="s">
+      <c r="M16" s="98" t="s">
         <v>222</v>
       </c>
-      <c r="T16" s="55" t="s">
+      <c r="N16" s="98" t="s">
         <v>222</v>
       </c>
-      <c r="U16" s="55" t="s">
+      <c r="O16" s="99" t="s">
         <v>222</v>
       </c>
-      <c r="V16" s="55" t="s">
+      <c r="P16" s="98" t="s">
         <v>222</v>
       </c>
-      <c r="W16" s="55" t="s">
-        <v>221</v>
-      </c>
-      <c r="X16" s="55" t="s">
-        <v>221</v>
-      </c>
-      <c r="Y16" s="55" t="s">
-        <v>196</v>
-      </c>
-      <c r="Z16" s="55" t="s">
-        <v>196</v>
-      </c>
-      <c r="AA16" s="55" t="s">
-        <v>196</v>
-      </c>
-      <c r="AB16" s="55" t="s">
-        <v>196</v>
-      </c>
-      <c r="AC16" s="55" t="s">
-        <v>196</v>
-      </c>
-      <c r="AD16" s="55" t="s">
-        <v>221</v>
-      </c>
-      <c r="AE16" s="55" t="s">
-        <v>221</v>
-      </c>
-      <c r="AF16" s="55" t="s">
-        <v>196</v>
-      </c>
-      <c r="AG16" s="55" t="s">
-        <v>196</v>
-      </c>
-      <c r="AH16" s="55" t="s">
-        <v>196</v>
-      </c>
-      <c r="AI16" s="55" t="s">
-        <v>196</v>
+      <c r="Q16" s="98" t="s">
+        <v>222</v>
+      </c>
+      <c r="R16" s="98" t="s">
+        <v>222</v>
+      </c>
+      <c r="S16" s="98" t="s">
+        <v>222</v>
+      </c>
+      <c r="T16" s="98" t="s">
+        <v>222</v>
+      </c>
+      <c r="U16" s="98" t="s">
+        <v>222</v>
+      </c>
+      <c r="V16" s="98" t="s">
+        <v>222</v>
+      </c>
+      <c r="W16" s="98" t="s">
+        <v>222</v>
+      </c>
+      <c r="X16" s="99" t="s">
+        <v>222</v>
+      </c>
+      <c r="Y16" s="98" t="s">
+        <v>222</v>
+      </c>
+      <c r="Z16" s="98" t="s">
+        <v>221</v>
+      </c>
+      <c r="AA16" s="98" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB16" s="98" t="s">
+        <v>196</v>
+      </c>
+      <c r="AC16" s="98" t="s">
+        <v>196</v>
+      </c>
+      <c r="AD16" s="98" t="s">
+        <v>197</v>
+      </c>
+      <c r="AE16" s="99" t="s">
+        <v>197</v>
+      </c>
+      <c r="AF16" s="99" t="s">
+        <v>220</v>
+      </c>
+      <c r="AG16" s="98" t="s">
+        <v>221</v>
+      </c>
+      <c r="AH16" s="98" t="s">
+        <v>221</v>
+      </c>
+      <c r="AI16" s="98" t="s">
+        <v>221</v>
       </c>
       <c r="AJ16" s="98"/>
       <c r="AL16" s="48">
@@ -15036,15 +16583,15 @@
       </c>
       <c r="AM16" s="48">
         <f>COUNTIF($F16:$AJ16,"M*")</f>
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="AN16" s="48">
         <f>COUNTIF($F16:$AJ16,"A*")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO16" s="48">
         <f>COUNTIF($F16:$AJ16,"N*")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AP16" s="48">
         <f>COUNTIF($F16:$AJ16,"O*")</f>
@@ -15363,7 +16910,7 @@
         <v>196</v>
       </c>
       <c r="Z19" s="95" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA19" s="95" t="s">
         <v>126</v>
@@ -15399,11 +16946,11 @@
       </c>
       <c r="AM19" s="48">
         <f t="shared" si="11"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AN19" s="48">
         <f t="shared" si="12"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO19" s="48">
         <f t="shared" si="13"/>
@@ -15714,13 +17261,13 @@
         <v>196</v>
       </c>
       <c r="V22" s="95" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="W22" s="95" t="s">
         <v>197</v>
       </c>
       <c r="X22" s="95" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="Y22" s="100" t="s">
         <v>220</v>
@@ -15762,7 +17309,7 @@
       </c>
       <c r="AM22" s="48">
         <f t="shared" si="11"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AN22" s="48">
         <f t="shared" si="12"/>
@@ -15770,7 +17317,7 @@
       </c>
       <c r="AO22" s="48">
         <f t="shared" si="13"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP22" s="48">
         <f t="shared" si="14"/>
@@ -16567,7 +18114,7 @@
         <v>197</v>
       </c>
       <c r="X29" s="102" t="s">
-        <v>220</v>
+        <v>197</v>
       </c>
       <c r="Y29" s="102" t="s">
         <v>220</v>
@@ -16613,11 +18160,11 @@
       </c>
       <c r="AN29" s="48">
         <f t="shared" si="12"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO29" s="48">
         <f t="shared" si="13"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AP29" s="48">
         <f t="shared" si="14"/>
@@ -17627,7 +19174,7 @@
         <v>221</v>
       </c>
       <c r="Q38" s="95" t="s">
-        <v>221</v>
+        <v>248</v>
       </c>
       <c r="R38" s="95" t="s">
         <v>196</v>
@@ -17648,10 +19195,10 @@
         <v>221</v>
       </c>
       <c r="X38" s="95" t="s">
-        <v>221</v>
+        <v>246</v>
       </c>
       <c r="Y38" s="95" t="s">
-        <v>221</v>
+        <v>248</v>
       </c>
       <c r="Z38" s="95" t="s">
         <v>196</v>
@@ -19536,7 +21083,7 @@
         <v>220</v>
       </c>
       <c r="T54" s="95" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="U54" s="95" t="s">
         <v>221</v>
@@ -19548,10 +21095,10 @@
         <v>221</v>
       </c>
       <c r="X54" s="95" t="s">
-        <v>196</v>
+        <v>222</v>
       </c>
       <c r="Y54" s="95" t="s">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="Z54" s="95" t="s">
         <v>197</v>
@@ -19590,15 +21137,15 @@
       </c>
       <c r="AM54" s="48">
         <f t="shared" si="16"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN54" s="48">
         <f t="shared" si="17"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO54" s="48">
         <f t="shared" si="18"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AP54" s="48">
         <f t="shared" si="19"/>
@@ -20499,7 +22046,7 @@
         <v>196</v>
       </c>
       <c r="U62" s="95" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="V62" s="95" t="s">
         <v>197</v>
@@ -20511,7 +22058,7 @@
         <v>220</v>
       </c>
       <c r="Y62" s="95" t="s">
-        <v>221</v>
+        <v>245</v>
       </c>
       <c r="Z62" s="93" t="s">
         <v>221</v>
@@ -20535,7 +22082,7 @@
         <v>220</v>
       </c>
       <c r="AG62" s="93" t="s">
-        <v>221</v>
+        <v>245</v>
       </c>
       <c r="AH62" s="93" t="s">
         <v>221</v>
@@ -20550,11 +22097,11 @@
       </c>
       <c r="AM62" s="48">
         <f t="shared" si="16"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AN62" s="48">
         <f t="shared" si="17"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO62" s="48">
         <f t="shared" si="18"/>
@@ -21252,7 +22799,7 @@
         <v>197</v>
       </c>
       <c r="AF68" s="94" t="s">
-        <v>220</v>
+        <v>197</v>
       </c>
       <c r="AG68" s="95" t="s">
         <v>220</v>
@@ -21274,11 +22821,11 @@
       </c>
       <c r="AN68" s="48">
         <f t="shared" si="17"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO68" s="48">
         <f t="shared" si="18"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP68" s="48">
         <f t="shared" si="19"/>
@@ -21468,7 +23015,7 @@
         <v>221</v>
       </c>
       <c r="X70" s="94" t="s">
-        <v>221</v>
+        <v>248</v>
       </c>
       <c r="Y70" s="95" t="s">
         <v>196</v>
@@ -21579,7 +23126,7 @@
         <v>197</v>
       </c>
       <c r="U71" s="94" t="s">
-        <v>220</v>
+        <v>197</v>
       </c>
       <c r="V71" s="95" t="s">
         <v>220</v>
@@ -21634,11 +23181,11 @@
       </c>
       <c r="AN71" s="48">
         <f t="shared" si="17"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO71" s="48">
         <f t="shared" si="18"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP71" s="48">
         <f t="shared" si="19"/>
@@ -21818,51 +23365,21 @@
       <c r="T73" s="95" t="s">
         <v>221</v>
       </c>
-      <c r="U73" s="93" t="s">
-        <v>196</v>
-      </c>
-      <c r="V73" s="93" t="s">
-        <v>196</v>
-      </c>
-      <c r="W73" s="93" t="s">
-        <v>197</v>
-      </c>
-      <c r="X73" s="93" t="s">
-        <v>197</v>
-      </c>
-      <c r="Y73" s="94" t="s">
-        <v>220</v>
-      </c>
-      <c r="Z73" s="95" t="s">
-        <v>221</v>
-      </c>
-      <c r="AA73" s="95" t="s">
-        <v>221</v>
-      </c>
-      <c r="AB73" s="95" t="s">
-        <v>221</v>
-      </c>
-      <c r="AC73" s="95" t="s">
-        <v>196</v>
-      </c>
-      <c r="AD73" s="93" t="s">
-        <v>196</v>
-      </c>
-      <c r="AE73" s="93" t="s">
-        <v>197</v>
-      </c>
-      <c r="AF73" s="93" t="s">
-        <v>197</v>
-      </c>
-      <c r="AG73" s="94" t="s">
-        <v>220</v>
-      </c>
-      <c r="AH73" s="95" t="s">
-        <v>221</v>
-      </c>
-      <c r="AI73" s="95" t="s">
-        <v>221</v>
-      </c>
+      <c r="U73" s="93"/>
+      <c r="V73" s="93"/>
+      <c r="W73" s="93"/>
+      <c r="X73" s="93"/>
+      <c r="Y73" s="94"/>
+      <c r="Z73" s="95"/>
+      <c r="AA73" s="95"/>
+      <c r="AB73" s="95"/>
+      <c r="AC73" s="95"/>
+      <c r="AD73" s="93"/>
+      <c r="AE73" s="93"/>
+      <c r="AF73" s="93"/>
+      <c r="AG73" s="94"/>
+      <c r="AH73" s="95"/>
+      <c r="AI73" s="95"/>
       <c r="AJ73" s="95"/>
       <c r="AL73" s="48">
         <f t="shared" si="15"/>
@@ -21870,19 +23387,19 @@
       </c>
       <c r="AM73" s="48">
         <f t="shared" si="16"/>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AN73" s="48">
         <f t="shared" si="17"/>
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AO73" s="48">
         <f t="shared" si="18"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AP73" s="48">
         <f t="shared" si="19"/>
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74" spans="2:42" ht="18.75" x14ac:dyDescent="0.25">
@@ -22065,7 +23582,7 @@
         <v>197</v>
       </c>
       <c r="W75" s="95" t="s">
-        <v>221</v>
+        <v>248</v>
       </c>
       <c r="X75" s="94" t="s">
         <v>221</v>
@@ -22086,7 +23603,7 @@
         <v>197</v>
       </c>
       <c r="AD75" s="95" t="s">
-        <v>221</v>
+        <v>246</v>
       </c>
       <c r="AE75" s="94" t="s">
         <v>221</v>
@@ -22186,11 +23703,11 @@
       <c r="E77" s="36"/>
       <c r="F77" s="37">
         <f t="shared" ref="F77:AJ77" si="25">COUNTIF(F10:F75,"M*")</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G77" s="37">
         <f t="shared" si="25"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H77" s="37">
         <f t="shared" si="25"/>
@@ -22206,11 +23723,11 @@
       </c>
       <c r="K77" s="37">
         <f t="shared" si="25"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L77" s="37">
         <f t="shared" si="25"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M77" s="37">
         <f t="shared" si="25"/>
@@ -22238,11 +23755,11 @@
       </c>
       <c r="S77" s="37">
         <f t="shared" si="25"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T77" s="37">
         <f t="shared" si="25"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="U77" s="37">
         <f t="shared" si="25"/>
@@ -22250,7 +23767,7 @@
       </c>
       <c r="V77" s="37">
         <f t="shared" si="25"/>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="W77" s="37">
         <f t="shared" si="25"/>
@@ -22258,7 +23775,7 @@
       </c>
       <c r="X77" s="37">
         <f t="shared" si="25"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y77" s="37">
         <f t="shared" si="25"/>
@@ -22266,11 +23783,11 @@
       </c>
       <c r="Z77" s="37">
         <f t="shared" si="25"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AA77" s="37">
         <f t="shared" si="25"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AB77" s="37">
         <f t="shared" si="25"/>
@@ -22282,7 +23799,7 @@
       </c>
       <c r="AD77" s="37">
         <f t="shared" si="25"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE77" s="37">
         <f t="shared" si="25"/>
@@ -22302,7 +23819,7 @@
       </c>
       <c r="AI77" s="37">
         <f t="shared" si="25"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ77" s="37">
         <f t="shared" si="25"/>
@@ -22337,7 +23854,7 @@
       <c r="E78" s="36"/>
       <c r="F78" s="37">
         <f t="shared" ref="F78:AJ78" si="26">COUNTIF(F10:F75,"A*")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G78" s="37">
         <f t="shared" si="26"/>
@@ -22365,11 +23882,11 @@
       </c>
       <c r="M78" s="37">
         <f t="shared" si="26"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N78" s="37">
         <f t="shared" si="26"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O78" s="37">
         <f t="shared" si="26"/>
@@ -22397,7 +23914,7 @@
       </c>
       <c r="U78" s="37">
         <f t="shared" si="26"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V78" s="37">
         <f t="shared" si="26"/>
@@ -22405,19 +23922,19 @@
       </c>
       <c r="W78" s="37">
         <f t="shared" si="26"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X78" s="37">
         <f t="shared" si="26"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y78" s="37">
         <f t="shared" si="26"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z78" s="37">
         <f t="shared" si="26"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA78" s="37">
         <f t="shared" si="26"/>
@@ -22429,7 +23946,7 @@
       </c>
       <c r="AC78" s="37">
         <f t="shared" si="26"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AD78" s="37">
         <f t="shared" si="26"/>
@@ -22492,11 +24009,11 @@
       </c>
       <c r="G79" s="37">
         <f t="shared" si="27"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H79" s="37">
         <f t="shared" si="27"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I79" s="37">
         <f t="shared" si="27"/>
@@ -22524,7 +24041,7 @@
       </c>
       <c r="O79" s="37">
         <f t="shared" si="27"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P79" s="37">
         <f t="shared" si="27"/>
@@ -22544,11 +24061,11 @@
       </c>
       <c r="T79" s="37">
         <f t="shared" si="27"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="U79" s="37">
         <f t="shared" si="27"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="V79" s="37">
         <f t="shared" si="27"/>
@@ -22556,7 +24073,7 @@
       </c>
       <c r="W79" s="37">
         <f t="shared" si="27"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="X79" s="37">
         <f t="shared" si="27"/>
@@ -22564,7 +24081,7 @@
       </c>
       <c r="Y79" s="37">
         <f t="shared" si="27"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z79" s="37">
         <f t="shared" si="27"/>
@@ -22588,7 +24105,7 @@
       </c>
       <c r="AE79" s="37">
         <f t="shared" si="27"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF79" s="37">
         <f t="shared" si="27"/>
@@ -22596,7 +24113,7 @@
       </c>
       <c r="AG79" s="37">
         <f t="shared" si="27"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH79" s="37">
         <f t="shared" si="27"/>
@@ -22719,15 +24236,15 @@
       </c>
       <c r="Z80" s="37">
         <f t="shared" si="28"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA80" s="37">
         <f t="shared" si="28"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AB80" s="37">
         <f t="shared" si="28"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AC80" s="37">
         <f t="shared" si="28"/>
@@ -22751,11 +24268,11 @@
       </c>
       <c r="AH80" s="37">
         <f t="shared" si="28"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI80" s="37">
         <f t="shared" si="28"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ80" s="37">
         <f t="shared" si="28"/>
@@ -22771,11 +24288,11 @@
       </c>
       <c r="AN80" s="48">
         <f t="shared" si="22"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO80" s="48">
         <f t="shared" si="23"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP80" s="48">
         <f t="shared" si="24"/>
@@ -23136,7 +24653,7 @@
       </c>
       <c r="Q83" s="50">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R83" s="50">
         <f t="shared" si="31"/>
@@ -23160,15 +24677,15 @@
       </c>
       <c r="W83" s="50">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X83" s="50">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y83" s="50">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z83" s="50">
         <f t="shared" si="31"/>
@@ -23188,7 +24705,7 @@
       </c>
       <c r="AD83" s="50">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE83" s="50">
         <f t="shared" si="31"/>
@@ -23200,7 +24717,7 @@
       </c>
       <c r="AG83" s="50">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH83" s="50">
         <f t="shared" si="31"/>
@@ -23224,11 +24741,11 @@
       </c>
       <c r="AN83" s="48">
         <f t="shared" si="22"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO83" s="48">
         <f t="shared" si="23"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP83" s="48">
         <f t="shared" si="24"/>
@@ -23307,7 +24824,7 @@
       </c>
       <c r="H85" s="41">
         <f t="shared" si="32"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I85" s="41">
         <f t="shared" si="32"/>
@@ -23319,23 +24836,23 @@
       </c>
       <c r="K85" s="41">
         <f t="shared" si="32"/>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L85" s="41">
         <f t="shared" si="32"/>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M85" s="41">
         <f t="shared" si="32"/>
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N85" s="41">
         <f t="shared" si="32"/>
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O85" s="41">
         <f t="shared" si="32"/>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P85" s="41">
         <f t="shared" si="32"/>
@@ -23351,31 +24868,31 @@
       </c>
       <c r="S85" s="41">
         <f t="shared" si="32"/>
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="T85" s="41">
         <f t="shared" si="32"/>
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="U85" s="41">
         <f t="shared" si="32"/>
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="V85" s="41">
         <f t="shared" si="32"/>
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="W85" s="41">
         <f t="shared" si="32"/>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="X85" s="41">
         <f t="shared" si="32"/>
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="Y85" s="41">
         <f t="shared" si="32"/>
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Z85" s="41">
         <f t="shared" si="32"/>
@@ -23383,7 +24900,7 @@
       </c>
       <c r="AA85" s="41">
         <f t="shared" si="32"/>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AB85" s="41">
         <f t="shared" si="32"/>
@@ -23391,15 +24908,15 @@
       </c>
       <c r="AC85" s="41">
         <f t="shared" si="32"/>
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AD85" s="41">
         <f t="shared" si="32"/>
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AE85" s="41">
         <f t="shared" si="32"/>
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AF85" s="41">
         <f t="shared" si="32"/>
@@ -23407,7 +24924,7 @@
       </c>
       <c r="AG85" s="41">
         <f t="shared" si="32"/>
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AH85" s="41">
         <f t="shared" si="32"/>
@@ -23415,7 +24932,7 @@
       </c>
       <c r="AI85" s="41">
         <f t="shared" si="32"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AJ85" s="41">
         <v>18</v>
@@ -23426,19 +24943,19 @@
       </c>
       <c r="AM85" s="48">
         <f t="shared" si="21"/>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AN85" s="48">
         <f t="shared" si="22"/>
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AO85" s="48">
         <f t="shared" si="23"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AP85" s="48">
         <f t="shared" si="24"/>
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="86" spans="3:42" ht="18.75" x14ac:dyDescent="0.3">
@@ -23577,7 +25094,7 @@
       </c>
       <c r="H87" s="37">
         <f t="shared" si="33"/>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I87" s="37">
         <f t="shared" si="33"/>
@@ -23589,23 +25106,23 @@
       </c>
       <c r="K87" s="37">
         <f t="shared" si="33"/>
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L87" s="37">
         <f t="shared" si="33"/>
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M87" s="37">
         <f t="shared" si="33"/>
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N87" s="37">
         <f t="shared" si="33"/>
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O87" s="37">
         <f t="shared" si="33"/>
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="P87" s="37">
         <f t="shared" si="33"/>
@@ -23621,55 +25138,55 @@
       </c>
       <c r="S87" s="37">
         <f t="shared" si="33"/>
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="T87" s="37">
         <f t="shared" si="33"/>
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="U87" s="37">
         <f t="shared" si="33"/>
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V87" s="37">
         <f t="shared" si="33"/>
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="W87" s="37">
         <f t="shared" si="33"/>
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="X87" s="37">
         <f t="shared" si="33"/>
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Y87" s="37">
         <f t="shared" si="33"/>
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="Z87" s="37">
         <f t="shared" si="33"/>
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AA87" s="37">
         <f t="shared" si="33"/>
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="AB87" s="37">
         <f t="shared" si="33"/>
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AC87" s="37">
         <f t="shared" si="33"/>
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AD87" s="37">
         <f t="shared" si="33"/>
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AE87" s="37">
         <f t="shared" si="33"/>
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AF87" s="37">
         <f t="shared" si="33"/>
@@ -23677,15 +25194,15 @@
       </c>
       <c r="AG87" s="37">
         <f t="shared" si="33"/>
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AH87" s="37">
         <f t="shared" si="33"/>
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AI87" s="37">
         <f t="shared" si="33"/>
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="AJ87" s="37">
         <v>35</v>
@@ -24044,384 +25561,457 @@
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="F76">
-    <cfRule type="containsText" dxfId="231" priority="127" operator="containsText" text="OFF">
+    <cfRule type="containsText" dxfId="396" priority="287" operator="containsText" text="OFF">
       <formula>NOT(ISERROR(SEARCH("OFF",F76)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="230" priority="126" operator="containsText" text="STNN21">
-      <formula>NOT(ISERROR(SEARCH("STNN21",F76)))</formula>
+    <cfRule type="containsText" dxfId="395" priority="284" operator="containsText" text="LV">
+      <formula>NOT(ISERROR(SEARCH("LV",F76)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="229" priority="117" operator="containsText" text="OT">
+    <cfRule type="containsText" dxfId="394" priority="283" operator="containsText" text="TR">
+      <formula>NOT(ISERROR(SEARCH("TR",F76)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="393" priority="278" operator="containsText" text="NN21">
+      <formula>NOT(ISERROR(SEARCH("NN21",F76)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="392" priority="282" operator="containsText" text="STAN13">
+      <formula>NOT(ISERROR(SEARCH("STAN13",F76)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="391" priority="277" operator="containsText" text="OT">
       <formula>NOT(ISERROR(SEARCH("OT",F76)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="228" priority="118" operator="containsText" text="NN21">
-      <formula>NOT(ISERROR(SEARCH("NN21",F76)))</formula>
+    <cfRule type="containsText" dxfId="390" priority="280" operator="containsText" text="MN06">
+      <formula>NOT(ISERROR(SEARCH("MN06",F76)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="227" priority="119" operator="containsText" text="AN13">
+    <cfRule type="containsText" dxfId="389" priority="279" operator="containsText" text="AN13">
       <formula>NOT(ISERROR(SEARCH("AN13",F76)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="226" priority="120" operator="containsText" text="MN06">
-      <formula>NOT(ISERROR(SEARCH("MN06",F76)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="225" priority="121" operator="containsText" text="STMN06">
+    <cfRule type="containsText" dxfId="388" priority="281" operator="containsText" text="STMN06">
       <formula>NOT(ISERROR(SEARCH("STMN06",F76)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="224" priority="122" operator="containsText" text="STAN13">
+    <cfRule type="containsText" dxfId="387" priority="285" operator="containsText" text="STAN13">
       <formula>NOT(ISERROR(SEARCH("STAN13",F76)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="223" priority="125" operator="containsText" text="STAN13">
-      <formula>NOT(ISERROR(SEARCH("STAN13",F76)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="222" priority="123" operator="containsText" text="TR">
-      <formula>NOT(ISERROR(SEARCH("TR",F76)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="221" priority="124" operator="containsText" text="LV">
-      <formula>NOT(ISERROR(SEARCH("LV",F76)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F10:AI10">
-    <cfRule type="containsText" dxfId="216" priority="53" operator="containsText" text="MN06">
-      <formula>NOT(ISERROR(SEARCH("MN06",F10)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="215" priority="55" operator="containsText" text="LV">
-      <formula>NOT(ISERROR(SEARCH("LV",F10)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="214" priority="56" operator="containsText" text="STNN21">
-      <formula>NOT(ISERROR(SEARCH("STNN21",F10)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="213" priority="57" operator="containsText" text="STAN13">
-      <formula>NOT(ISERROR(SEARCH("STAN13",F10)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="212" priority="58" operator="containsText" text="STMN06">
-      <formula>NOT(ISERROR(SEARCH("STMN06",F10)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="211" priority="59" operator="containsText" text="MN12">
-      <formula>NOT(ISERROR(SEARCH("MN12",F10)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="210" priority="60" operator="containsText" text="TR">
-      <formula>NOT(ISERROR(SEARCH("TR",F10)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="209" priority="61" operator="containsText" text="OFF">
-      <formula>NOT(ISERROR(SEARCH("OFF",F10)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F10:AI10">
-    <cfRule type="containsText" dxfId="208" priority="52" operator="containsText" text="NN21">
-      <formula>NOT(ISERROR(SEARCH("NN21",F10)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="207" priority="54" operator="containsText" text="AN13">
-      <formula>NOT(ISERROR(SEARCH("AN13",F10)))</formula>
+    <cfRule type="containsText" dxfId="386" priority="286" operator="containsText" text="STNN21">
+      <formula>NOT(ISERROR(SEARCH("STNN21",F76)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ5:AJ9">
-    <cfRule type="containsText" dxfId="181" priority="129" operator="containsText" text="AN13">
+    <cfRule type="containsText" dxfId="346" priority="162" operator="containsText" text="AN13">
       <formula>NOT(ISERROR(SEARCH("AN13",AJ5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="180" priority="128" operator="containsText" text="LV">
+    <cfRule type="containsText" dxfId="345" priority="161" operator="containsText" text="LV">
       <formula>NOT(ISERROR(SEARCH("LV",AJ5)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F10:AJ10 AJ11:AJ30">
-    <cfRule type="containsText" dxfId="179" priority="51" operator="containsText" text="OT">
-      <formula>NOT(ISERROR(SEARCH("OT",F10)))</formula>
+  <conditionalFormatting sqref="AJ10:AJ30">
+    <cfRule type="containsText" dxfId="344" priority="167" operator="containsText" text="OT">
+      <formula>NOT(ISERROR(SEARCH("OT",AJ10)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ62:AJ75">
-    <cfRule type="containsText" dxfId="178" priority="85" operator="containsText" text="MN06">
+    <cfRule type="containsText" dxfId="343" priority="201" operator="containsText" text="MN06">
       <formula>NOT(ISERROR(SEARCH("MN06",AJ62)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="177" priority="84" operator="containsText" text="OT">
+    <cfRule type="containsText" dxfId="342" priority="200" operator="containsText" text="OT">
       <formula>NOT(ISERROR(SEARCH("OT",AJ62)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ5:AJ9">
-    <cfRule type="containsText" dxfId="176" priority="194" operator="containsText" text="ME07">
+    <cfRule type="containsText" dxfId="341" priority="354" operator="containsText" text="ME07">
       <formula>NOT(ISERROR(SEARCH("ME07",AJ5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="175" priority="192" operator="containsText" text="TR">
+    <cfRule type="containsText" dxfId="340" priority="352" operator="containsText" text="TR">
       <formula>NOT(ISERROR(SEARCH("TR",AJ5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="174" priority="193" operator="containsText" text="OFF">
+    <cfRule type="containsText" dxfId="339" priority="353" operator="containsText" text="OFF">
       <formula>NOT(ISERROR(SEARCH("OFF",AJ5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ5:AJ15">
-    <cfRule type="containsText" dxfId="173" priority="191" operator="containsText" text="MN06">
+    <cfRule type="containsText" dxfId="338" priority="351" operator="containsText" text="MN06">
       <formula>NOT(ISERROR(SEARCH("MN06",AJ5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ10:AJ15">
-    <cfRule type="containsText" dxfId="172" priority="201" operator="containsText" text="STAN13">
+    <cfRule type="containsText" dxfId="337" priority="361" operator="containsText" text="STAN13">
       <formula>NOT(ISERROR(SEARCH("STAN13",AJ10)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="171" priority="199" operator="containsText" text="LV">
+    <cfRule type="containsText" dxfId="336" priority="359" operator="containsText" text="LV">
       <formula>NOT(ISERROR(SEARCH("LV",AJ10)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="170" priority="200" operator="containsText" text="STNN21">
+    <cfRule type="containsText" dxfId="335" priority="360" operator="containsText" text="STNN21">
       <formula>NOT(ISERROR(SEARCH("STNN21",AJ10)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="169" priority="205" operator="containsText" text="OFF">
+    <cfRule type="containsText" dxfId="334" priority="365" operator="containsText" text="OFF">
       <formula>NOT(ISERROR(SEARCH("OFF",AJ10)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="168" priority="204" operator="containsText" text="TR">
+    <cfRule type="containsText" dxfId="333" priority="364" operator="containsText" text="TR">
       <formula>NOT(ISERROR(SEARCH("TR",AJ10)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="167" priority="203" operator="containsText" text="MN12">
+    <cfRule type="containsText" dxfId="332" priority="363" operator="containsText" text="MN12">
       <formula>NOT(ISERROR(SEARCH("MN12",AJ10)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="166" priority="202" operator="containsText" text="STMN06">
+    <cfRule type="containsText" dxfId="331" priority="362" operator="containsText" text="STMN06">
       <formula>NOT(ISERROR(SEARCH("STMN06",AJ10)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ10:AJ61">
-    <cfRule type="containsText" dxfId="165" priority="198" operator="containsText" text="AN13">
+    <cfRule type="containsText" dxfId="330" priority="358" operator="containsText" text="AN13">
       <formula>NOT(ISERROR(SEARCH("AN13",AJ10)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ10:AJ75">
-    <cfRule type="containsText" dxfId="164" priority="180" operator="containsText" text="NN21">
+    <cfRule type="containsText" dxfId="329" priority="340" operator="containsText" text="NN21">
       <formula>NOT(ISERROR(SEARCH("NN21",AJ10)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ16:AJ30">
-    <cfRule type="containsText" dxfId="163" priority="210" operator="containsText" text="STMN06">
+    <cfRule type="containsText" dxfId="328" priority="370" operator="containsText" text="STMN06">
       <formula>NOT(ISERROR(SEARCH("STMN06",AJ16)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="162" priority="211" operator="containsText" text="STAN13">
+    <cfRule type="containsText" dxfId="327" priority="371" operator="containsText" text="STAN13">
       <formula>NOT(ISERROR(SEARCH("STAN13",AJ16)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="161" priority="212" operator="containsText" text="TR">
+    <cfRule type="containsText" dxfId="326" priority="372" operator="containsText" text="TR">
       <formula>NOT(ISERROR(SEARCH("TR",AJ16)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="160" priority="213" operator="containsText" text="LV">
+    <cfRule type="containsText" dxfId="325" priority="373" operator="containsText" text="LV">
       <formula>NOT(ISERROR(SEARCH("LV",AJ16)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="159" priority="214" operator="containsText" text="STAN13">
+    <cfRule type="containsText" dxfId="324" priority="374" operator="containsText" text="STAN13">
       <formula>NOT(ISERROR(SEARCH("STAN13",AJ16)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="158" priority="215" operator="containsText" text="STNN21">
+    <cfRule type="containsText" dxfId="323" priority="375" operator="containsText" text="STNN21">
       <formula>NOT(ISERROR(SEARCH("STNN21",AJ16)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="157" priority="216" operator="containsText" text="OFF">
+    <cfRule type="containsText" dxfId="322" priority="376" operator="containsText" text="OFF">
       <formula>NOT(ISERROR(SEARCH("OFF",AJ16)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ16:AJ61">
-    <cfRule type="containsText" dxfId="156" priority="209" operator="containsText" text="MN06">
+    <cfRule type="containsText" dxfId="321" priority="369" operator="containsText" text="MN06">
       <formula>NOT(ISERROR(SEARCH("MN06",AJ16)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ31:AJ61">
-    <cfRule type="containsText" dxfId="155" priority="220" operator="containsText" text="OT">
+    <cfRule type="containsText" dxfId="320" priority="380" operator="containsText" text="OT">
       <formula>NOT(ISERROR(SEARCH("OT",AJ31)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="154" priority="221" operator="containsText" text="MN12">
+    <cfRule type="containsText" dxfId="319" priority="381" operator="containsText" text="MN12">
       <formula>NOT(ISERROR(SEARCH("MN12",AJ31)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="153" priority="222" operator="containsText" text="STNN21">
+    <cfRule type="containsText" dxfId="318" priority="382" operator="containsText" text="STNN21">
       <formula>NOT(ISERROR(SEARCH("STNN21",AJ31)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="152" priority="223" operator="containsText" text="STAN13">
+    <cfRule type="containsText" dxfId="317" priority="383" operator="containsText" text="STAN13">
       <formula>NOT(ISERROR(SEARCH("STAN13",AJ31)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="151" priority="224" operator="containsText" text="STMN06">
+    <cfRule type="containsText" dxfId="316" priority="384" operator="containsText" text="STMN06">
       <formula>NOT(ISERROR(SEARCH("STMN06",AJ31)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="150" priority="225" operator="containsText" text="LV">
+    <cfRule type="containsText" dxfId="315" priority="385" operator="containsText" text="LV">
       <formula>NOT(ISERROR(SEARCH("LV",AJ31)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="149" priority="226" operator="containsText" text="TR">
+    <cfRule type="containsText" dxfId="314" priority="386" operator="containsText" text="TR">
       <formula>NOT(ISERROR(SEARCH("TR",AJ31)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="148" priority="227" operator="containsText" text="OFF">
+    <cfRule type="containsText" dxfId="313" priority="387" operator="containsText" text="OFF">
       <formula>NOT(ISERROR(SEARCH("OFF",AJ31)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ62:AJ75">
-    <cfRule type="containsText" dxfId="147" priority="181" operator="containsText" text="AN13">
+    <cfRule type="containsText" dxfId="312" priority="341" operator="containsText" text="AN13">
       <formula>NOT(ISERROR(SEARCH("AN13",AJ62)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="146" priority="182" operator="containsText" text="STMN06">
+    <cfRule type="containsText" dxfId="311" priority="342" operator="containsText" text="STMN06">
       <formula>NOT(ISERROR(SEARCH("STMN06",AJ62)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="145" priority="183" operator="containsText" text="STAN13">
+    <cfRule type="containsText" dxfId="310" priority="343" operator="containsText" text="STAN13">
       <formula>NOT(ISERROR(SEARCH("STAN13",AJ62)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="144" priority="184" operator="containsText" text="STNN21">
+    <cfRule type="containsText" dxfId="309" priority="344" operator="containsText" text="STNN21">
       <formula>NOT(ISERROR(SEARCH("STNN21",AJ62)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="143" priority="188" operator="containsText" text="OFF">
+    <cfRule type="containsText" dxfId="308" priority="348" operator="containsText" text="OFF">
       <formula>NOT(ISERROR(SEARCH("OFF",AJ62)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="142" priority="187" operator="containsText" text="NN13">
+    <cfRule type="containsText" dxfId="307" priority="347" operator="containsText" text="NN13">
       <formula>NOT(ISERROR(SEARCH("NN13",AJ62)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="141" priority="186" operator="containsText" text="TR">
+    <cfRule type="containsText" dxfId="306" priority="346" operator="containsText" text="TR">
       <formula>NOT(ISERROR(SEARCH("TR",AJ62)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="140" priority="185" operator="containsText" text="LV">
+    <cfRule type="containsText" dxfId="305" priority="345" operator="containsText" text="LV">
       <formula>NOT(ISERROR(SEARCH("LV",AJ62)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F62:AI75">
-    <cfRule type="containsText" dxfId="49" priority="40" operator="containsText" text="OT">
+  <conditionalFormatting sqref="F5:AI9">
+    <cfRule type="containsText" dxfId="82" priority="78" operator="containsText" text="LV">
+      <formula>NOT(ISERROR(SEARCH("LV",F5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="81" priority="79" operator="containsText" text="AN13">
+      <formula>NOT(ISERROR(SEARCH("AN13",F5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="80" priority="80" operator="containsText" text="MN06">
+      <formula>NOT(ISERROR(SEARCH("MN06",F5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="79" priority="81" operator="containsText" text="TR">
+      <formula>NOT(ISERROR(SEARCH("TR",F5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="78" priority="82" operator="containsText" text="OFF">
+      <formula>NOT(ISERROR(SEARCH("OFF",F5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="77" priority="83" operator="containsText" text="ME07">
+      <formula>NOT(ISERROR(SEARCH("ME07",F5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F62:S75">
+    <cfRule type="containsText" dxfId="76" priority="67" operator="containsText" text="OT">
       <formula>NOT(ISERROR(SEARCH("OT",F62)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="48" priority="41" operator="containsText" text="MN06">
+    <cfRule type="containsText" dxfId="75" priority="68" operator="containsText" text="MN06">
       <formula>NOT(ISERROR(SEARCH("MN06",F62)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="47" priority="42" operator="containsText" text="NN21">
+    <cfRule type="containsText" dxfId="74" priority="69" operator="containsText" text="NN21">
       <formula>NOT(ISERROR(SEARCH("NN21",F62)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="46" priority="43" operator="containsText" text="AN13">
+    <cfRule type="containsText" dxfId="73" priority="70" operator="containsText" text="AN13">
       <formula>NOT(ISERROR(SEARCH("AN13",F62)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="45" priority="44" operator="containsText" text="STMN06">
+    <cfRule type="containsText" dxfId="72" priority="71" operator="containsText" text="STMN06">
       <formula>NOT(ISERROR(SEARCH("STMN06",F62)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="44" priority="45" operator="containsText" text="STAN13">
+    <cfRule type="containsText" dxfId="71" priority="72" operator="containsText" text="STAN13">
       <formula>NOT(ISERROR(SEARCH("STAN13",F62)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="43" priority="46" operator="containsText" text="STNN21">
+    <cfRule type="containsText" dxfId="70" priority="73" operator="containsText" text="STNN21">
       <formula>NOT(ISERROR(SEARCH("STNN21",F62)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="42" priority="47" operator="containsText" text="LV">
+    <cfRule type="containsText" dxfId="69" priority="74" operator="containsText" text="LV">
       <formula>NOT(ISERROR(SEARCH("LV",F62)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="41" priority="48" operator="containsText" text="TR">
+    <cfRule type="containsText" dxfId="68" priority="75" operator="containsText" text="TR">
       <formula>NOT(ISERROR(SEARCH("TR",F62)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="40" priority="49" operator="containsText" text="NN13">
+    <cfRule type="containsText" dxfId="67" priority="76" operator="containsText" text="NN13">
       <formula>NOT(ISERROR(SEARCH("NN13",F62)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="39" priority="50" operator="containsText" text="OFF">
+    <cfRule type="containsText" dxfId="66" priority="77" operator="containsText" text="OFF">
       <formula>NOT(ISERROR(SEARCH("OFF",F62)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F31:AI61">
-    <cfRule type="containsText" dxfId="38" priority="29" operator="containsText" text="NN21">
+  <conditionalFormatting sqref="T62:AI75">
+    <cfRule type="containsText" dxfId="65" priority="56" operator="containsText" text="OT">
+      <formula>NOT(ISERROR(SEARCH("OT",T62)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="64" priority="57" operator="containsText" text="MN06">
+      <formula>NOT(ISERROR(SEARCH("MN06",T62)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="63" priority="58" operator="containsText" text="NN21">
+      <formula>NOT(ISERROR(SEARCH("NN21",T62)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="62" priority="59" operator="containsText" text="AN13">
+      <formula>NOT(ISERROR(SEARCH("AN13",T62)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="61" priority="60" operator="containsText" text="STMN06">
+      <formula>NOT(ISERROR(SEARCH("STMN06",T62)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="60" priority="61" operator="containsText" text="STAN13">
+      <formula>NOT(ISERROR(SEARCH("STAN13",T62)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="59" priority="62" operator="containsText" text="STNN21">
+      <formula>NOT(ISERROR(SEARCH("STNN21",T62)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="58" priority="63" operator="containsText" text="LV">
+      <formula>NOT(ISERROR(SEARCH("LV",T62)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="57" priority="64" operator="containsText" text="TR">
+      <formula>NOT(ISERROR(SEARCH("TR",T62)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="56" priority="65" operator="containsText" text="NN13">
+      <formula>NOT(ISERROR(SEARCH("NN13",T62)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="55" priority="66" operator="containsText" text="OFF">
+      <formula>NOT(ISERROR(SEARCH("OFF",T62)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F31:S61">
+    <cfRule type="containsText" dxfId="54" priority="45" operator="containsText" text="NN21">
       <formula>NOT(ISERROR(SEARCH("NN21",F31)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="37" priority="30" operator="containsText" text="AN13">
+    <cfRule type="containsText" dxfId="53" priority="46" operator="containsText" text="AN13">
       <formula>NOT(ISERROR(SEARCH("AN13",F31)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="36" priority="31" operator="containsText" text="MN06">
+    <cfRule type="containsText" dxfId="52" priority="47" operator="containsText" text="MN06">
       <formula>NOT(ISERROR(SEARCH("MN06",F31)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="35" priority="32" operator="containsText" text="OT">
+    <cfRule type="containsText" dxfId="51" priority="48" operator="containsText" text="OT">
       <formula>NOT(ISERROR(SEARCH("OT",F31)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="34" priority="33" operator="containsText" text="MN12">
+    <cfRule type="containsText" dxfId="50" priority="49" operator="containsText" text="MN12">
       <formula>NOT(ISERROR(SEARCH("MN12",F31)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="33" priority="34" operator="containsText" text="STNN21">
+    <cfRule type="containsText" dxfId="49" priority="50" operator="containsText" text="STNN21">
       <formula>NOT(ISERROR(SEARCH("STNN21",F31)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="32" priority="35" operator="containsText" text="STAN13">
+    <cfRule type="containsText" dxfId="48" priority="51" operator="containsText" text="STAN13">
       <formula>NOT(ISERROR(SEARCH("STAN13",F31)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="31" priority="36" operator="containsText" text="STMN06">
+    <cfRule type="containsText" dxfId="47" priority="52" operator="containsText" text="STMN06">
       <formula>NOT(ISERROR(SEARCH("STMN06",F31)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="30" priority="37" operator="containsText" text="LV">
+    <cfRule type="containsText" dxfId="46" priority="53" operator="containsText" text="LV">
       <formula>NOT(ISERROR(SEARCH("LV",F31)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="29" priority="38" operator="containsText" text="TR">
+    <cfRule type="containsText" dxfId="45" priority="54" operator="containsText" text="TR">
       <formula>NOT(ISERROR(SEARCH("TR",F31)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="28" priority="39" operator="containsText" text="OFF">
+    <cfRule type="containsText" dxfId="44" priority="55" operator="containsText" text="OFF">
       <formula>NOT(ISERROR(SEARCH("OFF",F31)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F17:AI30">
-    <cfRule type="containsText" dxfId="27" priority="23" operator="containsText" text="STAN13">
-      <formula>NOT(ISERROR(SEARCH("STAN13",F17)))</formula>
+  <conditionalFormatting sqref="T31:AI61">
+    <cfRule type="containsText" dxfId="43" priority="34" operator="containsText" text="NN21">
+      <formula>NOT(ISERROR(SEARCH("NN21",T31)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="26" priority="24" operator="containsText" text="TR">
-      <formula>NOT(ISERROR(SEARCH("TR",F17)))</formula>
+    <cfRule type="containsText" dxfId="42" priority="35" operator="containsText" text="AN13">
+      <formula>NOT(ISERROR(SEARCH("AN13",T31)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="25" priority="25" operator="containsText" text="LV">
-      <formula>NOT(ISERROR(SEARCH("LV",F17)))</formula>
+    <cfRule type="containsText" dxfId="41" priority="36" operator="containsText" text="MN06">
+      <formula>NOT(ISERROR(SEARCH("MN06",T31)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="24" priority="27" operator="containsText" text="STNN21">
-      <formula>NOT(ISERROR(SEARCH("STNN21",F17)))</formula>
+    <cfRule type="containsText" dxfId="40" priority="37" operator="containsText" text="OT">
+      <formula>NOT(ISERROR(SEARCH("OT",T31)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="23" priority="28" operator="containsText" text="OFF">
-      <formula>NOT(ISERROR(SEARCH("OFF",F17)))</formula>
+    <cfRule type="containsText" dxfId="39" priority="38" operator="containsText" text="MN12">
+      <formula>NOT(ISERROR(SEARCH("MN12",T31)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="38" priority="39" operator="containsText" text="STNN21">
+      <formula>NOT(ISERROR(SEARCH("STNN21",T31)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="37" priority="40" operator="containsText" text="STAN13">
+      <formula>NOT(ISERROR(SEARCH("STAN13",T31)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="36" priority="41" operator="containsText" text="STMN06">
+      <formula>NOT(ISERROR(SEARCH("STMN06",T31)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="35" priority="42" operator="containsText" text="LV">
+      <formula>NOT(ISERROR(SEARCH("LV",T31)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="34" priority="43" operator="containsText" text="TR">
+      <formula>NOT(ISERROR(SEARCH("TR",T31)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="33" priority="44" operator="containsText" text="OFF">
+      <formula>NOT(ISERROR(SEARCH("OFF",T31)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F17:AI30">
-    <cfRule type="containsText" dxfId="22" priority="18" operator="containsText" text="OT">
-      <formula>NOT(ISERROR(SEARCH("OT",F17)))</formula>
+  <conditionalFormatting sqref="F16:S30">
+    <cfRule type="containsText" dxfId="32" priority="28" operator="containsText" text="STAN13">
+      <formula>NOT(ISERROR(SEARCH("STAN13",F16)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="21" priority="19" operator="containsText" text="NN21">
-      <formula>NOT(ISERROR(SEARCH("NN21",F17)))</formula>
+    <cfRule type="containsText" dxfId="31" priority="29" operator="containsText" text="TR">
+      <formula>NOT(ISERROR(SEARCH("TR",F16)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="20" priority="20" operator="containsText" text="AN13">
-      <formula>NOT(ISERROR(SEARCH("AN13",F17)))</formula>
+    <cfRule type="containsText" dxfId="30" priority="30" operator="containsText" text="LV">
+      <formula>NOT(ISERROR(SEARCH("LV",F16)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="19" priority="21" operator="containsText" text="MN06">
-      <formula>NOT(ISERROR(SEARCH("MN06",F17)))</formula>
+    <cfRule type="containsText" dxfId="29" priority="32" operator="containsText" text="STNN21">
+      <formula>NOT(ISERROR(SEARCH("STNN21",F16)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="22" operator="containsText" text="STMN06">
-      <formula>NOT(ISERROR(SEARCH("STMN06",F17)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="17" priority="26" operator="containsText" text="STAN13">
-      <formula>NOT(ISERROR(SEARCH("STAN13",F17)))</formula>
+    <cfRule type="containsText" dxfId="28" priority="33" operator="containsText" text="OFF">
+      <formula>NOT(ISERROR(SEARCH("OFF",F16)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F11:AI16">
-    <cfRule type="containsText" dxfId="16" priority="7" operator="containsText" text="OT">
-      <formula>NOT(ISERROR(SEARCH("OT",F11)))</formula>
+  <conditionalFormatting sqref="F16:S30">
+    <cfRule type="containsText" dxfId="27" priority="23" operator="containsText" text="OT">
+      <formula>NOT(ISERROR(SEARCH("OT",F16)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="15" priority="8" operator="containsText" text="NN21">
-      <formula>NOT(ISERROR(SEARCH("NN21",F11)))</formula>
+    <cfRule type="containsText" dxfId="26" priority="24" operator="containsText" text="NN21">
+      <formula>NOT(ISERROR(SEARCH("NN21",F16)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="9" operator="containsText" text="MN06">
-      <formula>NOT(ISERROR(SEARCH("MN06",F11)))</formula>
+    <cfRule type="containsText" dxfId="25" priority="25" operator="containsText" text="AN13">
+      <formula>NOT(ISERROR(SEARCH("AN13",F16)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="13" priority="10" operator="containsText" text="AN13">
-      <formula>NOT(ISERROR(SEARCH("AN13",F11)))</formula>
+    <cfRule type="containsText" dxfId="24" priority="26" operator="containsText" text="MN06">
+      <formula>NOT(ISERROR(SEARCH("MN06",F16)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="11" operator="containsText" text="LV">
-      <formula>NOT(ISERROR(SEARCH("LV",F11)))</formula>
+    <cfRule type="containsText" dxfId="23" priority="27" operator="containsText" text="STMN06">
+      <formula>NOT(ISERROR(SEARCH("STMN06",F16)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="11" priority="12" operator="containsText" text="STNN21">
-      <formula>NOT(ISERROR(SEARCH("STNN21",F11)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="13" operator="containsText" text="STAN13">
-      <formula>NOT(ISERROR(SEARCH("STAN13",F11)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="9" priority="14" operator="containsText" text="STMN06">
-      <formula>NOT(ISERROR(SEARCH("STMN06",F11)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="15" operator="containsText" text="MN12">
-      <formula>NOT(ISERROR(SEARCH("MN12",F11)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="7" priority="16" operator="containsText" text="TR">
-      <formula>NOT(ISERROR(SEARCH("TR",F11)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="17" operator="containsText" text="OFF">
-      <formula>NOT(ISERROR(SEARCH("OFF",F11)))</formula>
+    <cfRule type="containsText" dxfId="22" priority="31" operator="containsText" text="STAN13">
+      <formula>NOT(ISERROR(SEARCH("STAN13",F16)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:AI9">
-    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="LV">
-      <formula>NOT(ISERROR(SEARCH("LV",F5)))</formula>
+  <conditionalFormatting sqref="T16:AI30">
+    <cfRule type="containsText" dxfId="21" priority="17" operator="containsText" text="STAN13">
+      <formula>NOT(ISERROR(SEARCH("STAN13",T16)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="AN13">
-      <formula>NOT(ISERROR(SEARCH("AN13",F5)))</formula>
+    <cfRule type="containsText" dxfId="20" priority="18" operator="containsText" text="TR">
+      <formula>NOT(ISERROR(SEARCH("TR",T16)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="MN06">
-      <formula>NOT(ISERROR(SEARCH("MN06",F5)))</formula>
+    <cfRule type="containsText" dxfId="19" priority="19" operator="containsText" text="LV">
+      <formula>NOT(ISERROR(SEARCH("LV",T16)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="TR">
-      <formula>NOT(ISERROR(SEARCH("TR",F5)))</formula>
+    <cfRule type="containsText" dxfId="18" priority="21" operator="containsText" text="STNN21">
+      <formula>NOT(ISERROR(SEARCH("STNN21",T16)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="5" operator="containsText" text="OFF">
-      <formula>NOT(ISERROR(SEARCH("OFF",F5)))</formula>
+    <cfRule type="containsText" dxfId="17" priority="22" operator="containsText" text="OFF">
+      <formula>NOT(ISERROR(SEARCH("OFF",T16)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="6" operator="containsText" text="ME07">
-      <formula>NOT(ISERROR(SEARCH("ME07",F5)))</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T16:AI30">
+    <cfRule type="containsText" dxfId="16" priority="12" operator="containsText" text="OT">
+      <formula>NOT(ISERROR(SEARCH("OT",T16)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="15" priority="13" operator="containsText" text="NN21">
+      <formula>NOT(ISERROR(SEARCH("NN21",T16)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="14" priority="14" operator="containsText" text="AN13">
+      <formula>NOT(ISERROR(SEARCH("AN13",T16)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="13" priority="15" operator="containsText" text="MN06">
+      <formula>NOT(ISERROR(SEARCH("MN06",T16)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="12" priority="16" operator="containsText" text="STMN06">
+      <formula>NOT(ISERROR(SEARCH("STMN06",T16)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="11" priority="20" operator="containsText" text="STAN13">
+      <formula>NOT(ISERROR(SEARCH("STAN13",T16)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F10:AI15">
+    <cfRule type="containsText" dxfId="10" priority="1" operator="containsText" text="OT">
+      <formula>NOT(ISERROR(SEARCH("OT",F10)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="9" priority="2" operator="containsText" text="NN21">
+      <formula>NOT(ISERROR(SEARCH("NN21",F10)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="8" priority="3" operator="containsText" text="MN06">
+      <formula>NOT(ISERROR(SEARCH("MN06",F10)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="7" priority="4" operator="containsText" text="AN13">
+      <formula>NOT(ISERROR(SEARCH("AN13",F10)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="6" priority="5" operator="containsText" text="LV">
+      <formula>NOT(ISERROR(SEARCH("LV",F10)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="5" priority="6" operator="containsText" text="STNN21">
+      <formula>NOT(ISERROR(SEARCH("STNN21",F10)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="7" operator="containsText" text="STAN13">
+      <formula>NOT(ISERROR(SEARCH("STAN13",F10)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="8" operator="containsText" text="STMN06">
+      <formula>NOT(ISERROR(SEARCH("STMN06",F10)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="9" operator="containsText" text="MN12">
+      <formula>NOT(ISERROR(SEARCH("MN12",F10)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="10" operator="containsText" text="TR">
+      <formula>NOT(ISERROR(SEARCH("TR",F10)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="11" operator="containsText" text="OFF">
+      <formula>NOT(ISERROR(SEARCH("OFF",F10)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -26766,22 +28356,22 @@
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="F5:AJ9">
-    <cfRule type="containsText" dxfId="139" priority="1" operator="containsText" text="LV">
+    <cfRule type="containsText" dxfId="304" priority="1" operator="containsText" text="LV">
       <formula>NOT(ISERROR(SEARCH("LV",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="138" priority="2" operator="containsText" text="AN13">
+    <cfRule type="containsText" dxfId="303" priority="2" operator="containsText" text="AN13">
       <formula>NOT(ISERROR(SEARCH("AN13",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="137" priority="3" operator="containsText" text="MN06">
+    <cfRule type="containsText" dxfId="302" priority="3" operator="containsText" text="MN06">
       <formula>NOT(ISERROR(SEARCH("MN06",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="136" priority="5" operator="containsText" text="TR">
+    <cfRule type="containsText" dxfId="301" priority="5" operator="containsText" text="TR">
       <formula>NOT(ISERROR(SEARCH("TR",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="135" priority="8" operator="containsText" text="OFF">
+    <cfRule type="containsText" dxfId="300" priority="8" operator="containsText" text="OFF">
       <formula>NOT(ISERROR(SEARCH("OFF",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="134" priority="9" operator="containsText" text="ME07">
+    <cfRule type="containsText" dxfId="299" priority="9" operator="containsText" text="ME07">
       <formula>NOT(ISERROR(SEARCH("ME07",F5)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29352,37 +30942,37 @@
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="F5:AJ10">
-    <cfRule type="containsText" dxfId="133" priority="2" operator="containsText" text="OT">
+    <cfRule type="containsText" dxfId="298" priority="2" operator="containsText" text="OT">
       <formula>NOT(ISERROR(SEARCH("OT",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="132" priority="3" operator="containsText" text="NN21">
+    <cfRule type="containsText" dxfId="297" priority="3" operator="containsText" text="NN21">
       <formula>NOT(ISERROR(SEARCH("NN21",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="131" priority="4" operator="containsText" text="MN06">
+    <cfRule type="containsText" dxfId="296" priority="4" operator="containsText" text="MN06">
       <formula>NOT(ISERROR(SEARCH("MN06",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="130" priority="5" operator="containsText" text="AN13">
+    <cfRule type="containsText" dxfId="295" priority="5" operator="containsText" text="AN13">
       <formula>NOT(ISERROR(SEARCH("AN13",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="129" priority="6" operator="containsText" text="LV">
+    <cfRule type="containsText" dxfId="294" priority="6" operator="containsText" text="LV">
       <formula>NOT(ISERROR(SEARCH("LV",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="128" priority="7" operator="containsText" text="STNN21">
+    <cfRule type="containsText" dxfId="293" priority="7" operator="containsText" text="STNN21">
       <formula>NOT(ISERROR(SEARCH("STNN21",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="127" priority="8" operator="containsText" text="STAN13">
+    <cfRule type="containsText" dxfId="292" priority="8" operator="containsText" text="STAN13">
       <formula>NOT(ISERROR(SEARCH("STAN13",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="126" priority="9" operator="containsText" text="STMN06">
+    <cfRule type="containsText" dxfId="291" priority="9" operator="containsText" text="STMN06">
       <formula>NOT(ISERROR(SEARCH("STMN06",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="125" priority="10" operator="containsText" text="MN12">
+    <cfRule type="containsText" dxfId="290" priority="10" operator="containsText" text="MN12">
       <formula>NOT(ISERROR(SEARCH("MN12",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="124" priority="11" operator="containsText" text="TR">
+    <cfRule type="containsText" dxfId="289" priority="11" operator="containsText" text="TR">
       <formula>NOT(ISERROR(SEARCH("TR",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="123" priority="12" operator="containsText" text="OFF">
+    <cfRule type="containsText" dxfId="288" priority="12" operator="containsText" text="OFF">
       <formula>NOT(ISERROR(SEARCH("OFF",F5)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29718,28 +31308,28 @@
         <v>222</v>
       </c>
       <c r="R5" s="98" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="S5" s="98" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="T5" s="98" t="s">
-        <v>196</v>
+        <v>222</v>
       </c>
       <c r="U5" s="98" t="s">
-        <v>196</v>
+        <v>222</v>
       </c>
       <c r="V5" s="98" t="s">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="W5" s="98" t="s">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="X5" s="99" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Y5" s="98" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Z5" s="98" t="s">
         <v>221</v>
@@ -29778,19 +31368,19 @@
       </c>
       <c r="AM5" s="48">
         <f>COUNTIF($F5:$AJ5,"M*")</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AN5" s="48">
         <f>COUNTIF($F5:$AJ5,"A*")</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AO5" s="48">
         <f>COUNTIF($F5:$AJ5,"N*")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP5" s="48">
         <f>COUNTIF($F5:$AJ5,"O*")</f>
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="2:42" ht="18.75" x14ac:dyDescent="0.25">
@@ -30102,7 +31692,7 @@
         <v>196</v>
       </c>
       <c r="Z8" s="95" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA8" s="95" t="s">
         <v>126</v>
@@ -30138,11 +31728,11 @@
       </c>
       <c r="AM8" s="48">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AN8" s="48">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO8" s="48">
         <f t="shared" si="3"/>
@@ -30450,13 +32040,13 @@
         <v>196</v>
       </c>
       <c r="V11" s="95" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="W11" s="95" t="s">
         <v>197</v>
       </c>
       <c r="X11" s="95" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="Y11" s="100" t="s">
         <v>220</v>
@@ -30498,7 +32088,7 @@
       </c>
       <c r="AM11" s="48">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AN11" s="48">
         <f t="shared" si="2"/>
@@ -30506,7 +32096,7 @@
       </c>
       <c r="AO11" s="48">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP11" s="48">
         <f t="shared" si="4"/>
@@ -31296,7 +32886,7 @@
         <v>197</v>
       </c>
       <c r="X18" s="102" t="s">
-        <v>220</v>
+        <v>197</v>
       </c>
       <c r="Y18" s="102" t="s">
         <v>220</v>
@@ -31342,11 +32932,11 @@
       </c>
       <c r="AN18" s="48">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO18" s="48">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AP18" s="48">
         <f t="shared" si="4"/>
@@ -31572,15 +33162,15 @@
       </c>
       <c r="T21" s="37">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U21" s="37">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V21" s="37">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W21" s="37">
         <f t="shared" si="5"/>
@@ -31596,7 +33186,7 @@
       </c>
       <c r="Z21" s="37">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA21" s="37">
         <f t="shared" si="5"/>
@@ -31714,7 +33304,7 @@
       </c>
       <c r="W22" s="37">
         <f t="shared" si="6"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X22" s="37">
         <f t="shared" si="6"/>
@@ -31726,7 +33316,7 @@
       </c>
       <c r="Z22" s="37">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA22" s="37">
         <f t="shared" si="6"/>
@@ -31848,7 +33438,7 @@
       </c>
       <c r="X23" s="37">
         <f t="shared" si="7"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y23" s="37">
         <f t="shared" si="7"/>
@@ -31954,11 +33544,11 @@
       </c>
       <c r="R24" s="37">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S24" s="37">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T24" s="37">
         <f t="shared" si="8"/>
@@ -31982,7 +33572,7 @@
       </c>
       <c r="Y24" s="37">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z24" s="37">
         <f t="shared" si="8"/>
@@ -32389,23 +33979,23 @@
       </c>
       <c r="T28" s="41">
         <f t="shared" si="11"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U28" s="41">
         <f t="shared" si="11"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V28" s="41">
         <f t="shared" si="11"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W28" s="41">
         <f t="shared" si="11"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X28" s="41">
         <f t="shared" si="11"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y28" s="41">
         <f t="shared" si="11"/>
@@ -32611,35 +34201,35 @@
       </c>
       <c r="R30" s="37">
         <f t="shared" si="12"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="S30" s="37">
         <f t="shared" si="12"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T30" s="37">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="U30" s="37">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V30" s="37">
         <f t="shared" si="12"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W30" s="37">
         <f t="shared" si="12"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="X30" s="37">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y30" s="37">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z30" s="37">
         <f t="shared" si="12"/>
@@ -32913,45 +34503,45 @@
     <mergeCell ref="C8:D8"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
-  <conditionalFormatting sqref="F5:AI19">
-    <cfRule type="containsText" dxfId="122" priority="7" operator="containsText" text="STAN13">
+  <conditionalFormatting sqref="F5:S19">
+    <cfRule type="containsText" dxfId="287" priority="18" operator="containsText" text="STAN13">
       <formula>NOT(ISERROR(SEARCH("STAN13",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="121" priority="8" operator="containsText" text="TR">
+    <cfRule type="containsText" dxfId="286" priority="19" operator="containsText" text="TR">
       <formula>NOT(ISERROR(SEARCH("TR",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="120" priority="9" operator="containsText" text="LV">
+    <cfRule type="containsText" dxfId="285" priority="20" operator="containsText" text="LV">
       <formula>NOT(ISERROR(SEARCH("LV",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="119" priority="11" operator="containsText" text="STNN21">
+    <cfRule type="containsText" dxfId="284" priority="22" operator="containsText" text="STNN21">
       <formula>NOT(ISERROR(SEARCH("STNN21",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="118" priority="12" operator="containsText" text="OFF">
+    <cfRule type="containsText" dxfId="283" priority="23" operator="containsText" text="OFF">
       <formula>NOT(ISERROR(SEARCH("OFF",F5)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:AJ19">
-    <cfRule type="containsText" dxfId="117" priority="2" operator="containsText" text="OT">
+  <conditionalFormatting sqref="F5:S19 AJ5:AJ19">
+    <cfRule type="containsText" dxfId="282" priority="13" operator="containsText" text="OT">
       <formula>NOT(ISERROR(SEARCH("OT",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="116" priority="3" operator="containsText" text="NN21">
+    <cfRule type="containsText" dxfId="281" priority="14" operator="containsText" text="NN21">
       <formula>NOT(ISERROR(SEARCH("NN21",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="115" priority="4" operator="containsText" text="AN13">
+    <cfRule type="containsText" dxfId="280" priority="15" operator="containsText" text="AN13">
       <formula>NOT(ISERROR(SEARCH("AN13",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="114" priority="5" operator="containsText" text="MN06">
+    <cfRule type="containsText" dxfId="279" priority="16" operator="containsText" text="MN06">
       <formula>NOT(ISERROR(SEARCH("MN06",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="113" priority="6" operator="containsText" text="STMN06">
+    <cfRule type="containsText" dxfId="278" priority="17" operator="containsText" text="STMN06">
       <formula>NOT(ISERROR(SEARCH("STMN06",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="112" priority="10" operator="containsText" text="STAN13">
+    <cfRule type="containsText" dxfId="277" priority="21" operator="containsText" text="STAN13">
       <formula>NOT(ISERROR(SEARCH("STAN13",F5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F26:AJ26">
-    <cfRule type="colorScale" priority="1">
+    <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -32963,20 +34553,57 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ5:AJ19">
-    <cfRule type="containsText" dxfId="111" priority="21" operator="containsText" text="TR">
+    <cfRule type="containsText" dxfId="276" priority="32" operator="containsText" text="TR">
       <formula>NOT(ISERROR(SEARCH("TR",AJ5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="110" priority="22" operator="containsText" text="LV">
+    <cfRule type="containsText" dxfId="275" priority="33" operator="containsText" text="LV">
       <formula>NOT(ISERROR(SEARCH("LV",AJ5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="109" priority="27" operator="containsText" text="STAN13">
+    <cfRule type="containsText" dxfId="274" priority="38" operator="containsText" text="STAN13">
       <formula>NOT(ISERROR(SEARCH("STAN13",AJ5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="108" priority="28" operator="containsText" text="STNN21">
+    <cfRule type="containsText" dxfId="273" priority="39" operator="containsText" text="STNN21">
       <formula>NOT(ISERROR(SEARCH("STNN21",AJ5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="107" priority="30" operator="containsText" text="OFF">
+    <cfRule type="containsText" dxfId="272" priority="41" operator="containsText" text="OFF">
       <formula>NOT(ISERROR(SEARCH("OFF",AJ5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T5:AI19">
+    <cfRule type="containsText" dxfId="192" priority="6" operator="containsText" text="STAN13">
+      <formula>NOT(ISERROR(SEARCH("STAN13",T5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="191" priority="7" operator="containsText" text="TR">
+      <formula>NOT(ISERROR(SEARCH("TR",T5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="190" priority="8" operator="containsText" text="LV">
+      <formula>NOT(ISERROR(SEARCH("LV",T5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="189" priority="10" operator="containsText" text="STNN21">
+      <formula>NOT(ISERROR(SEARCH("STNN21",T5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="188" priority="11" operator="containsText" text="OFF">
+      <formula>NOT(ISERROR(SEARCH("OFF",T5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T5:AI19">
+    <cfRule type="containsText" dxfId="187" priority="1" operator="containsText" text="OT">
+      <formula>NOT(ISERROR(SEARCH("OT",T5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="186" priority="2" operator="containsText" text="NN21">
+      <formula>NOT(ISERROR(SEARCH("NN21",T5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="185" priority="3" operator="containsText" text="AN13">
+      <formula>NOT(ISERROR(SEARCH("AN13",T5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="184" priority="4" operator="containsText" text="MN06">
+      <formula>NOT(ISERROR(SEARCH("MN06",T5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="183" priority="5" operator="containsText" text="STMN06">
+      <formula>NOT(ISERROR(SEARCH("STMN06",T5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="182" priority="9" operator="containsText" text="STAN13">
+      <formula>NOT(ISERROR(SEARCH("STAN13",T5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -34141,7 +35768,7 @@
         <v>221</v>
       </c>
       <c r="Q12" s="95" t="s">
-        <v>221</v>
+        <v>248</v>
       </c>
       <c r="R12" s="95" t="s">
         <v>196</v>
@@ -34162,10 +35789,10 @@
         <v>221</v>
       </c>
       <c r="X12" s="95" t="s">
-        <v>221</v>
+        <v>246</v>
       </c>
       <c r="Y12" s="95" t="s">
-        <v>221</v>
+        <v>248</v>
       </c>
       <c r="Z12" s="95" t="s">
         <v>196</v>
@@ -36050,7 +37677,7 @@
         <v>220</v>
       </c>
       <c r="T28" s="95" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="U28" s="95" t="s">
         <v>221</v>
@@ -36062,10 +37689,10 @@
         <v>221</v>
       </c>
       <c r="X28" s="95" t="s">
-        <v>196</v>
+        <v>222</v>
       </c>
       <c r="Y28" s="95" t="s">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="Z28" s="95" t="s">
         <v>197</v>
@@ -36104,15 +37731,15 @@
       </c>
       <c r="AM28" s="48">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN28" s="48">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO28" s="48">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AP28" s="48">
         <f t="shared" si="4"/>
@@ -37073,7 +38700,7 @@
       </c>
       <c r="X37" s="37">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y37" s="37">
         <f t="shared" si="5"/>
@@ -37208,7 +38835,7 @@
       </c>
       <c r="Y38" s="37">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z38" s="37">
         <f t="shared" si="6"/>
@@ -37319,7 +38946,7 @@
       </c>
       <c r="T39" s="37">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U39" s="37">
         <f t="shared" si="7"/>
@@ -37386,7 +39013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="2:42" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:42" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C40" s="180" t="s">
         <v>73</v>
       </c>
@@ -37831,7 +39458,7 @@
       </c>
       <c r="Q43" s="126">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R43" s="126">
         <f t="shared" si="11"/>
@@ -37859,11 +39486,11 @@
       </c>
       <c r="X43" s="126">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y43" s="126">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z43" s="126">
         <f t="shared" si="11"/>
@@ -38010,7 +39637,7 @@
       </c>
       <c r="T45" s="41">
         <f t="shared" si="12"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="U45" s="41">
         <f t="shared" si="12"/>
@@ -38026,11 +39653,11 @@
       </c>
       <c r="X45" s="41">
         <f t="shared" si="12"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y45" s="41">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z45" s="41">
         <f t="shared" si="12"/>
@@ -38240,7 +39867,7 @@
       </c>
       <c r="T47" s="37">
         <f t="shared" si="13"/>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="U47" s="37">
         <f t="shared" si="13"/>
@@ -38256,11 +39883,11 @@
       </c>
       <c r="X47" s="37">
         <f t="shared" si="13"/>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y47" s="37">
         <f t="shared" si="13"/>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z47" s="37">
         <f t="shared" si="13"/>
@@ -38552,43 +40179,43 @@
     <mergeCell ref="B3:D4"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
-  <conditionalFormatting sqref="F5:AJ35">
-    <cfRule type="containsText" dxfId="106" priority="2" operator="containsText" text="NN21">
+  <conditionalFormatting sqref="F5:S35 AJ5:AJ35">
+    <cfRule type="containsText" dxfId="271" priority="13" operator="containsText" text="NN21">
       <formula>NOT(ISERROR(SEARCH("NN21",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="105" priority="3" operator="containsText" text="AN13">
+    <cfRule type="containsText" dxfId="270" priority="14" operator="containsText" text="AN13">
       <formula>NOT(ISERROR(SEARCH("AN13",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="104" priority="4" operator="containsText" text="MN06">
+    <cfRule type="containsText" dxfId="269" priority="15" operator="containsText" text="MN06">
       <formula>NOT(ISERROR(SEARCH("MN06",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="103" priority="5" operator="containsText" text="OT">
+    <cfRule type="containsText" dxfId="268" priority="16" operator="containsText" text="OT">
       <formula>NOT(ISERROR(SEARCH("OT",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="102" priority="6" operator="containsText" text="MN12">
+    <cfRule type="containsText" dxfId="267" priority="17" operator="containsText" text="MN12">
       <formula>NOT(ISERROR(SEARCH("MN12",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="101" priority="7" operator="containsText" text="STNN21">
+    <cfRule type="containsText" dxfId="266" priority="18" operator="containsText" text="STNN21">
       <formula>NOT(ISERROR(SEARCH("STNN21",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="100" priority="8" operator="containsText" text="STAN13">
+    <cfRule type="containsText" dxfId="265" priority="19" operator="containsText" text="STAN13">
       <formula>NOT(ISERROR(SEARCH("STAN13",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="99" priority="9" operator="containsText" text="STMN06">
+    <cfRule type="containsText" dxfId="264" priority="20" operator="containsText" text="STMN06">
       <formula>NOT(ISERROR(SEARCH("STMN06",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="98" priority="10" operator="containsText" text="LV">
+    <cfRule type="containsText" dxfId="263" priority="21" operator="containsText" text="LV">
       <formula>NOT(ISERROR(SEARCH("LV",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="97" priority="11" operator="containsText" text="TR">
+    <cfRule type="containsText" dxfId="262" priority="22" operator="containsText" text="TR">
       <formula>NOT(ISERROR(SEARCH("TR",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="96" priority="12" operator="containsText" text="OFF">
+    <cfRule type="containsText" dxfId="261" priority="23" operator="containsText" text="OFF">
       <formula>NOT(ISERROR(SEARCH("OFF",F5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F43:AJ43">
-    <cfRule type="colorScale" priority="1">
+    <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -38597,6 +40224,41 @@
         <color rgb="FFFCFCFF"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T5:AI35">
+    <cfRule type="containsText" dxfId="203" priority="1" operator="containsText" text="NN21">
+      <formula>NOT(ISERROR(SEARCH("NN21",T5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="202" priority="2" operator="containsText" text="AN13">
+      <formula>NOT(ISERROR(SEARCH("AN13",T5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="201" priority="3" operator="containsText" text="MN06">
+      <formula>NOT(ISERROR(SEARCH("MN06",T5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="200" priority="4" operator="containsText" text="OT">
+      <formula>NOT(ISERROR(SEARCH("OT",T5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="199" priority="5" operator="containsText" text="MN12">
+      <formula>NOT(ISERROR(SEARCH("MN12",T5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="198" priority="6" operator="containsText" text="STNN21">
+      <formula>NOT(ISERROR(SEARCH("STNN21",T5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="197" priority="7" operator="containsText" text="STAN13">
+      <formula>NOT(ISERROR(SEARCH("STAN13",T5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="196" priority="8" operator="containsText" text="STMN06">
+      <formula>NOT(ISERROR(SEARCH("STMN06",T5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="195" priority="9" operator="containsText" text="LV">
+      <formula>NOT(ISERROR(SEARCH("LV",T5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="194" priority="10" operator="containsText" text="TR">
+      <formula>NOT(ISERROR(SEARCH("TR",T5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="193" priority="11" operator="containsText" text="OFF">
+      <formula>NOT(ISERROR(SEARCH("OFF",T5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -38928,7 +40590,7 @@
         <v>196</v>
       </c>
       <c r="U5" s="95" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="V5" s="95" t="s">
         <v>197</v>
@@ -38940,7 +40602,7 @@
         <v>220</v>
       </c>
       <c r="Y5" s="95" t="s">
-        <v>221</v>
+        <v>245</v>
       </c>
       <c r="Z5" s="93" t="s">
         <v>221</v>
@@ -38964,7 +40626,7 @@
         <v>220</v>
       </c>
       <c r="AG5" s="93" t="s">
-        <v>221</v>
+        <v>245</v>
       </c>
       <c r="AH5" s="93" t="s">
         <v>221</v>
@@ -38979,11 +40641,11 @@
       </c>
       <c r="AM5" s="22">
         <f t="shared" ref="AM5:AM18" si="1">COUNTIF($F5:$AJ5,"M*")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AN5" s="22">
         <f t="shared" ref="AN5:AN18" si="2">COUNTIF($F5:$AJ5,"A*")</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO5" s="22">
         <f t="shared" ref="AO5:AO18" si="3">COUNTIF($F5:$AJ5,"N*")</f>
@@ -39666,7 +41328,7 @@
         <v>197</v>
       </c>
       <c r="AF11" s="94" t="s">
-        <v>220</v>
+        <v>197</v>
       </c>
       <c r="AG11" s="95" t="s">
         <v>220</v>
@@ -39688,11 +41350,11 @@
       </c>
       <c r="AN11" s="22">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO11" s="22">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP11" s="22">
         <f t="shared" si="4"/>
@@ -39882,7 +41544,7 @@
         <v>221</v>
       </c>
       <c r="X13" s="94" t="s">
-        <v>221</v>
+        <v>248</v>
       </c>
       <c r="Y13" s="95" t="s">
         <v>196</v>
@@ -39993,7 +41655,7 @@
         <v>197</v>
       </c>
       <c r="U14" s="94" t="s">
-        <v>220</v>
+        <v>197</v>
       </c>
       <c r="V14" s="95" t="s">
         <v>220</v>
@@ -40048,11 +41710,11 @@
       </c>
       <c r="AN14" s="22">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO14" s="22">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP14" s="22">
         <f t="shared" si="4"/>
@@ -40232,51 +41894,21 @@
       <c r="T16" s="95" t="s">
         <v>221</v>
       </c>
-      <c r="U16" s="93" t="s">
-        <v>196</v>
-      </c>
-      <c r="V16" s="93" t="s">
-        <v>196</v>
-      </c>
-      <c r="W16" s="93" t="s">
-        <v>197</v>
-      </c>
-      <c r="X16" s="93" t="s">
-        <v>197</v>
-      </c>
-      <c r="Y16" s="94" t="s">
-        <v>220</v>
-      </c>
-      <c r="Z16" s="95" t="s">
-        <v>221</v>
-      </c>
-      <c r="AA16" s="95" t="s">
-        <v>221</v>
-      </c>
-      <c r="AB16" s="95" t="s">
-        <v>221</v>
-      </c>
-      <c r="AC16" s="95" t="s">
-        <v>196</v>
-      </c>
-      <c r="AD16" s="93" t="s">
-        <v>196</v>
-      </c>
-      <c r="AE16" s="93" t="s">
-        <v>197</v>
-      </c>
-      <c r="AF16" s="93" t="s">
-        <v>197</v>
-      </c>
-      <c r="AG16" s="94" t="s">
-        <v>220</v>
-      </c>
-      <c r="AH16" s="95" t="s">
-        <v>221</v>
-      </c>
-      <c r="AI16" s="95" t="s">
-        <v>221</v>
-      </c>
+      <c r="U16" s="93"/>
+      <c r="V16" s="93"/>
+      <c r="W16" s="93"/>
+      <c r="X16" s="93"/>
+      <c r="Y16" s="94"/>
+      <c r="Z16" s="95"/>
+      <c r="AA16" s="95"/>
+      <c r="AB16" s="95"/>
+      <c r="AC16" s="95"/>
+      <c r="AD16" s="93"/>
+      <c r="AE16" s="93"/>
+      <c r="AF16" s="93"/>
+      <c r="AG16" s="94"/>
+      <c r="AH16" s="95"/>
+      <c r="AI16" s="95"/>
       <c r="AJ16" s="95"/>
       <c r="AL16" s="22">
         <f t="shared" si="0"/>
@@ -40284,19 +41916,19 @@
       </c>
       <c r="AM16" s="22">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AN16" s="22">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AO16" s="22">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AP16" s="22">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="2:42" ht="18.75" x14ac:dyDescent="0.25">
@@ -40479,7 +42111,7 @@
         <v>197</v>
       </c>
       <c r="W18" s="95" t="s">
-        <v>221</v>
+        <v>248</v>
       </c>
       <c r="X18" s="94" t="s">
         <v>221</v>
@@ -40500,7 +42132,7 @@
         <v>197</v>
       </c>
       <c r="AD18" s="95" t="s">
-        <v>221</v>
+        <v>246</v>
       </c>
       <c r="AE18" s="94" t="s">
         <v>221</v>
@@ -40645,7 +42277,7 @@
       </c>
       <c r="V20" s="37">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W20" s="37">
         <f t="shared" si="5"/>
@@ -40673,11 +42305,11 @@
       </c>
       <c r="AC20" s="37">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD20" s="37">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE20" s="37">
         <f t="shared" si="5"/>
@@ -40780,11 +42412,11 @@
       </c>
       <c r="W21" s="37">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X21" s="37">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y21" s="37">
         <f t="shared" si="6"/>
@@ -40812,7 +42444,7 @@
       </c>
       <c r="AE21" s="37">
         <f t="shared" si="6"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF21" s="37">
         <f t="shared" si="6"/>
@@ -40903,7 +42535,7 @@
       </c>
       <c r="U22" s="37">
         <f t="shared" si="7"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V22" s="37">
         <f t="shared" si="7"/>
@@ -40919,7 +42551,7 @@
       </c>
       <c r="Y22" s="37">
         <f t="shared" si="7"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z22" s="37">
         <f t="shared" si="7"/>
@@ -40947,11 +42579,11 @@
       </c>
       <c r="AF22" s="37">
         <f t="shared" si="7"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG22" s="37">
         <f t="shared" si="7"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH22" s="37">
         <f t="shared" si="7"/>
@@ -41054,15 +42686,15 @@
       </c>
       <c r="Z23" s="37">
         <f t="shared" si="8"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA23" s="37">
         <f t="shared" si="8"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AB23" s="37">
         <f t="shared" si="8"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC23" s="37">
         <f t="shared" si="8"/>
@@ -41086,11 +42718,11 @@
       </c>
       <c r="AH23" s="37">
         <f t="shared" si="8"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI23" s="37">
         <f t="shared" si="8"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AJ23" s="37">
         <f t="shared" si="8"/>
@@ -41435,15 +43067,15 @@
       </c>
       <c r="W26" s="126">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X26" s="126">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y26" s="126">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z26" s="126">
         <f t="shared" si="11"/>
@@ -41463,7 +43095,7 @@
       </c>
       <c r="AD26" s="126">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE26" s="126">
         <f t="shared" si="11"/>
@@ -41475,7 +43107,7 @@
       </c>
       <c r="AG26" s="126">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH26" s="126">
         <f t="shared" si="11"/>
@@ -41594,23 +43226,23 @@
       </c>
       <c r="U28" s="41">
         <f t="shared" si="12"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V28" s="41">
         <f t="shared" si="12"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W28" s="41">
         <f t="shared" si="12"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X28" s="41">
         <f t="shared" si="12"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y28" s="41">
         <f t="shared" si="12"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z28" s="41">
         <f t="shared" si="12"/>
@@ -41626,23 +43258,23 @@
       </c>
       <c r="AC28" s="41">
         <f t="shared" si="12"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD28" s="41">
         <f t="shared" si="12"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE28" s="41">
         <f t="shared" si="12"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF28" s="41">
         <f t="shared" si="12"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG28" s="41">
         <f t="shared" si="12"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH28" s="41">
         <f t="shared" si="12"/>
@@ -41825,63 +43457,63 @@
       </c>
       <c r="U30" s="37">
         <f t="shared" si="13"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V30" s="37">
         <f t="shared" si="13"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W30" s="37">
         <f t="shared" si="13"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="X30" s="37">
         <f t="shared" si="13"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y30" s="37">
         <f t="shared" si="13"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z30" s="37">
         <f t="shared" si="13"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AA30" s="37">
         <f t="shared" si="13"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AB30" s="37">
         <f t="shared" si="13"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC30" s="37">
         <f t="shared" si="13"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AD30" s="37">
         <f t="shared" si="13"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE30" s="37">
         <f t="shared" si="13"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF30" s="37">
         <f t="shared" si="13"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG30" s="37">
         <f t="shared" si="13"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH30" s="37">
         <f t="shared" si="13"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI30" s="37">
         <f t="shared" si="13"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AJ30" s="37">
         <f t="shared" si="13"/>
@@ -42115,43 +43747,43 @@
     <mergeCell ref="AO2:AO4"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
-  <conditionalFormatting sqref="F5:AJ18">
-    <cfRule type="containsText" dxfId="95" priority="2" operator="containsText" text="OT">
+  <conditionalFormatting sqref="F5:S18 AJ5:AJ18">
+    <cfRule type="containsText" dxfId="260" priority="13" operator="containsText" text="OT">
       <formula>NOT(ISERROR(SEARCH("OT",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="94" priority="3" operator="containsText" text="MN06">
+    <cfRule type="containsText" dxfId="259" priority="14" operator="containsText" text="MN06">
       <formula>NOT(ISERROR(SEARCH("MN06",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="93" priority="4" operator="containsText" text="NN21">
+    <cfRule type="containsText" dxfId="258" priority="15" operator="containsText" text="NN21">
       <formula>NOT(ISERROR(SEARCH("NN21",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="92" priority="5" operator="containsText" text="AN13">
+    <cfRule type="containsText" dxfId="257" priority="16" operator="containsText" text="AN13">
       <formula>NOT(ISERROR(SEARCH("AN13",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="91" priority="6" operator="containsText" text="STMN06">
+    <cfRule type="containsText" dxfId="256" priority="17" operator="containsText" text="STMN06">
       <formula>NOT(ISERROR(SEARCH("STMN06",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="90" priority="7" operator="containsText" text="STAN13">
+    <cfRule type="containsText" dxfId="255" priority="18" operator="containsText" text="STAN13">
       <formula>NOT(ISERROR(SEARCH("STAN13",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="89" priority="8" operator="containsText" text="STNN21">
+    <cfRule type="containsText" dxfId="254" priority="19" operator="containsText" text="STNN21">
       <formula>NOT(ISERROR(SEARCH("STNN21",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="88" priority="9" operator="containsText" text="LV">
+    <cfRule type="containsText" dxfId="253" priority="20" operator="containsText" text="LV">
       <formula>NOT(ISERROR(SEARCH("LV",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="87" priority="10" operator="containsText" text="TR">
+    <cfRule type="containsText" dxfId="252" priority="21" operator="containsText" text="TR">
       <formula>NOT(ISERROR(SEARCH("TR",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="86" priority="11" operator="containsText" text="NN13">
+    <cfRule type="containsText" dxfId="251" priority="22" operator="containsText" text="NN13">
       <formula>NOT(ISERROR(SEARCH("NN13",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="85" priority="12" operator="containsText" text="OFF">
+    <cfRule type="containsText" dxfId="250" priority="23" operator="containsText" text="OFF">
       <formula>NOT(ISERROR(SEARCH("OFF",F5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F26:AJ26">
-    <cfRule type="colorScale" priority="1">
+    <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -42160,6 +43792,41 @@
         <color rgb="FFFCFCFF"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T5:AI18">
+    <cfRule type="containsText" dxfId="214" priority="1" operator="containsText" text="OT">
+      <formula>NOT(ISERROR(SEARCH("OT",T5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="213" priority="2" operator="containsText" text="MN06">
+      <formula>NOT(ISERROR(SEARCH("MN06",T5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="212" priority="3" operator="containsText" text="NN21">
+      <formula>NOT(ISERROR(SEARCH("NN21",T5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="211" priority="4" operator="containsText" text="AN13">
+      <formula>NOT(ISERROR(SEARCH("AN13",T5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="210" priority="5" operator="containsText" text="STMN06">
+      <formula>NOT(ISERROR(SEARCH("STMN06",T5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="209" priority="6" operator="containsText" text="STAN13">
+      <formula>NOT(ISERROR(SEARCH("STAN13",T5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="208" priority="7" operator="containsText" text="STNN21">
+      <formula>NOT(ISERROR(SEARCH("STNN21",T5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="207" priority="8" operator="containsText" text="LV">
+      <formula>NOT(ISERROR(SEARCH("LV",T5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="206" priority="9" operator="containsText" text="TR">
+      <formula>NOT(ISERROR(SEARCH("TR",T5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="205" priority="10" operator="containsText" text="NN13">
+      <formula>NOT(ISERROR(SEARCH("NN13",T5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="204" priority="11" operator="containsText" text="OFF">
+      <formula>NOT(ISERROR(SEARCH("OFF",T5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -44933,117 +46600,117 @@
     <mergeCell ref="B8:C8"/>
   </mergeCells>
   <conditionalFormatting sqref="E5:AH10">
-    <cfRule type="containsText" dxfId="84" priority="23" operator="containsText" text="STN">
+    <cfRule type="containsText" dxfId="249" priority="23" operator="containsText" text="STN">
       <formula>NOT(ISERROR(SEARCH("STN",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="83" priority="24" operator="containsText" text="STN">
+    <cfRule type="containsText" dxfId="248" priority="24" operator="containsText" text="STN">
       <formula>NOT(ISERROR(SEARCH("STN",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="82" priority="25" operator="containsText" text="STM">
+    <cfRule type="containsText" dxfId="247" priority="25" operator="containsText" text="STM">
       <formula>NOT(ISERROR(SEARCH("STM",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="81" priority="26" operator="containsText" text="M">
+    <cfRule type="containsText" dxfId="246" priority="26" operator="containsText" text="M">
       <formula>NOT(ISERROR(SEARCH("M",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="80" priority="27" operator="containsText" text="STM1">
+    <cfRule type="containsText" dxfId="245" priority="27" operator="containsText" text="STM1">
       <formula>NOT(ISERROR(SEARCH("STM1",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="79" priority="28" operator="containsText" text="M">
+    <cfRule type="containsText" dxfId="244" priority="28" operator="containsText" text="M">
       <formula>NOT(ISERROR(SEARCH("M",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="78" priority="29" operator="containsText" text="STM">
+    <cfRule type="containsText" dxfId="243" priority="29" operator="containsText" text="STM">
       <formula>NOT(ISERROR(SEARCH("STM",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="77" priority="30" operator="containsText" text="STM">
+    <cfRule type="containsText" dxfId="242" priority="30" operator="containsText" text="STM">
       <formula>NOT(ISERROR(SEARCH("STM",E5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5:AH15">
-    <cfRule type="containsText" dxfId="76" priority="19" operator="containsText" text="A">
+    <cfRule type="containsText" dxfId="241" priority="19" operator="containsText" text="A">
       <formula>NOT(ISERROR(SEARCH("A",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="75" priority="5" operator="containsText" text="STM1">
+    <cfRule type="containsText" dxfId="240" priority="5" operator="containsText" text="STM1">
       <formula>NOT(ISERROR(SEARCH("STM1",E5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E11:AH15">
-    <cfRule type="containsText" dxfId="74" priority="16" operator="containsText" text="STM1">
+    <cfRule type="containsText" dxfId="239" priority="16" operator="containsText" text="STM1">
       <formula>NOT(ISERROR(SEARCH("STM1",E11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="73" priority="17" operator="containsText" text="O">
+    <cfRule type="containsText" dxfId="238" priority="17" operator="containsText" text="O">
       <formula>NOT(ISERROR(SEARCH("O",E11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="72" priority="18" operator="containsText" text="N">
+    <cfRule type="containsText" dxfId="237" priority="18" operator="containsText" text="N">
       <formula>NOT(ISERROR(SEARCH("N",E11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="71" priority="6" operator="containsText" text="STN">
+    <cfRule type="containsText" dxfId="236" priority="6" operator="containsText" text="STN">
       <formula>NOT(ISERROR(SEARCH("STN",E11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="70" priority="7" operator="containsText" text="STN">
+    <cfRule type="containsText" dxfId="235" priority="7" operator="containsText" text="STN">
       <formula>NOT(ISERROR(SEARCH("STN",E11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="69" priority="8" operator="containsText" text="STM">
+    <cfRule type="containsText" dxfId="234" priority="8" operator="containsText" text="STM">
       <formula>NOT(ISERROR(SEARCH("STM",E11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="68" priority="9" operator="containsText" text="M">
+    <cfRule type="containsText" dxfId="233" priority="9" operator="containsText" text="M">
       <formula>NOT(ISERROR(SEARCH("M",E11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="67" priority="10" operator="containsText" text="STM1">
+    <cfRule type="containsText" dxfId="232" priority="10" operator="containsText" text="STM1">
       <formula>NOT(ISERROR(SEARCH("STM1",E11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="66" priority="11" operator="containsText" text="M">
+    <cfRule type="containsText" dxfId="231" priority="11" operator="containsText" text="M">
       <formula>NOT(ISERROR(SEARCH("M",E11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="65" priority="12" operator="containsText" text="STM">
+    <cfRule type="containsText" dxfId="230" priority="12" operator="containsText" text="STM">
       <formula>NOT(ISERROR(SEARCH("STM",E11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="64" priority="13" operator="containsText" text="STM">
+    <cfRule type="containsText" dxfId="229" priority="13" operator="containsText" text="STM">
       <formula>NOT(ISERROR(SEARCH("STM",E11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="63" priority="14" operator="containsText" text="STM1">
+    <cfRule type="containsText" dxfId="228" priority="14" operator="containsText" text="STM1">
       <formula>NOT(ISERROR(SEARCH("STM1",E11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="62" priority="15" operator="containsText" text="STA">
+    <cfRule type="containsText" dxfId="227" priority="15" operator="containsText" text="STA">
       <formula>NOT(ISERROR(SEARCH("STA",E11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="61" priority="20" operator="containsText" text="M">
+    <cfRule type="containsText" dxfId="226" priority="20" operator="containsText" text="M">
       <formula>NOT(ISERROR(SEARCH("M",E11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5:AI15">
-    <cfRule type="containsText" dxfId="60" priority="3" operator="containsText" text="STM1">
+    <cfRule type="containsText" dxfId="225" priority="3" operator="containsText" text="STM1">
       <formula>NOT(ISERROR(SEARCH("STM1",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="59" priority="4" operator="containsText" text="STM1">
+    <cfRule type="containsText" dxfId="224" priority="4" operator="containsText" text="STM1">
       <formula>NOT(ISERROR(SEARCH("STM1",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="58" priority="1" operator="containsText" text="STN">
+    <cfRule type="containsText" dxfId="223" priority="1" operator="containsText" text="STN">
       <formula>NOT(ISERROR(SEARCH("STN",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="57" priority="2" operator="containsText" text="STA">
+    <cfRule type="containsText" dxfId="222" priority="2" operator="containsText" text="STA">
       <formula>NOT(ISERROR(SEARCH("STA",E5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:AH5 E6:AH10">
-    <cfRule type="containsText" dxfId="56" priority="31" operator="containsText" text="STM1">
+    <cfRule type="containsText" dxfId="221" priority="31" operator="containsText" text="STM1">
       <formula>NOT(ISERROR(SEARCH("STM1",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="55" priority="32" operator="containsText" text="STA">
+    <cfRule type="containsText" dxfId="220" priority="32" operator="containsText" text="STA">
       <formula>NOT(ISERROR(SEARCH("STA",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="54" priority="33" operator="containsText" text="STM1">
+    <cfRule type="containsText" dxfId="219" priority="33" operator="containsText" text="STM1">
       <formula>NOT(ISERROR(SEARCH("STM1",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="53" priority="34" operator="containsText" text="O">
+    <cfRule type="containsText" dxfId="218" priority="34" operator="containsText" text="O">
       <formula>NOT(ISERROR(SEARCH("O",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="52" priority="35" operator="containsText" text="N">
+    <cfRule type="containsText" dxfId="217" priority="35" operator="containsText" text="N">
       <formula>NOT(ISERROR(SEARCH("N",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="51" priority="36" operator="containsText" text="A">
+    <cfRule type="containsText" dxfId="216" priority="36" operator="containsText" text="A">
       <formula>NOT(ISERROR(SEARCH("A",E5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="50" priority="37" operator="containsText" text="M">
+    <cfRule type="containsText" dxfId="215" priority="37" operator="containsText" text="M">
       <formula>NOT(ISERROR(SEARCH("M",E5)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -45083,15 +46750,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
@@ -45101,7 +46759,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="مستند" ma:contentTypeID="0x01010053585A714B17B949862FA1B71BD97610" ma:contentTypeVersion="21" ma:contentTypeDescription="إنشاء مستند جديد." ma:contentTypeScope="" ma:versionID="26eaa5d39eda60f8775bd022d70769f0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns3="f1e9c892-1499-41bb-8a64-60ef909d8682" xmlns:ns4="0ecd8b7c-869e-4f04-a6a3-066c3c63b311" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5c2899f3b08a11c7878800e445033e12" ns1:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -45377,15 +47035,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7131BC6-00FD-4253-878E-994124306B86}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04335F04-3ECE-4043-846B-35335B1D83ED}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
@@ -45403,7 +47062,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBA6F5DD-99D5-4C0F-817B-85F132A9EB4D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -45423,6 +47082,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7131BC6-00FD-4253-878E-994124306B86}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{456ceee3-7fed-44e8-a399-cd4111988137}" enabled="0" method="" siteId="{456ceee3-7fed-44e8-a399-cd4111988137}" removed="1"/>
